--- a/Parkview_Crossing_Acquisition_Model.xlsx
+++ b/Parkview_Crossing_Acquisition_Model.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="540">
   <si>
     <t xml:space="preserve">ASSUMPTIONS — Parkview Crossing, 901-951 NW 8th Ave, Pompano Beach, FL 33060</t>
   </si>
@@ -795,13 +795,13 @@
     <t xml:space="preserve">EXIT VALUATION — tax-adjusted</t>
   </si>
   <si>
-    <t xml:space="preserve">Entry Cap Rate (Year-1 model NOI / Purchase Price)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exit Cap Rate — base case (entry + 50bps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exit Cap Rate — sensitivity ceiling (entry + 100bps)</t>
+    <t xml:space="preserve">Entry Cap Rate ANCHOR for exit-spread convention = #2 above: In-Place, Day-0, reassessed tax (primary/cost-of-sale method)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit Cap Rate — base case (in-place entry + 50bps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit Cap Rate — sensitivity ceiling (in-place entry + 100bps)</t>
   </si>
   <si>
     <t xml:space="preserve">Effective Tax Rate at Exit (same cost-of-sale factor as entry)</t>
@@ -984,6 +984,12 @@
     <t xml:space="preserve">Sponsor Equity</t>
   </si>
   <si>
+    <t xml:space="preserve">  LP Equity (90%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  GP Equity (10%, co-invest)</t>
+  </si>
+  <si>
     <t xml:space="preserve">  memo: vs. Scenario B equity</t>
   </si>
   <si>
@@ -1014,13 +1020,13 @@
     <t xml:space="preserve">Year-1 Cash-on-Cash</t>
   </si>
   <si>
-    <t xml:space="preserve">WATERFALL — 8% Pref -&gt; ROC -&gt; 70/30 to 12% IRR -&gt; 50/50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Method: each tier tracks a compounding 'hurdle balance' (what LP is owed at that tier's rate) that is debited by every LP dollar received. The balance hitting zero is mathematically equivalent to LP achieving exactly that IRR — no iterative solver needed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Available Cash for Distribution</t>
+    <t xml:space="preserve">WATERFALL — 8% Pref -&gt; ROC -&gt; 70/30 to 12% IRR -&gt; 50/50 (BASE CASE: Scenario A, assumed debt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method: each tier tracks a compounding 'hurdle balance' (what LP is owed at that tier's rate) that is debited by every LP dollar received. The balance hitting zero is mathematically equivalent to LP achieving exactly that IRR — no iterative solver needed. Runs on Scenario A (assumed debt, the base case) -- for the Scenario B (new debt) waterfall, swap the 'Available Cash' and equity references below to the 'Returns' / 'Capital' tabs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Available Cash for Distribution (Scenario A)</t>
   </si>
   <si>
     <t xml:space="preserve">LP Investment / GP Investment (Year 0)</t>
@@ -1491,7 +1497,10 @@
     <t xml:space="preserve">6. LP EQUITY + GP EQUITY = TOTAL EQUITY</t>
   </si>
   <si>
-    <t xml:space="preserve">LP+GP Equity - Total Equity</t>
+    <t xml:space="preserve">Scenario B (Capital tab): LP+GP Equity - Total Equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario A (base case, Returns (Assumed) tab): LP+GP Equity - Total Equity</t>
   </si>
   <si>
     <t xml:space="preserve">7. DEBT SCHEDULE INTERNAL CONSISTENCY</t>
@@ -1524,16 +1533,13 @@
     <t xml:space="preserve">97-unit garden apartment community, Pompano Beach, FL, built 1958. Light value-add / core-plus: 75% of units already renovated by the prior owner; this plan finishes the remaining ~24 classic units, burns off loss-to-lease on the rest, and underwrites Florida's post-sale property-tax reassessment (and a tax-adjusted exit) explicitly rather than ignoring them.</t>
   </si>
   <si>
-    <t xml:space="preserve">SOURCES &amp; USES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Uses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Loan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  LP Equity (90%)</t>
+    <t xml:space="preserve">SOURCES &amp; USES — BASE CASE: Scenario A, assumed debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Uses (incl. loan assumption fee)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumed Debt (First + Supplemental, Year-0)</t>
   </si>
   <si>
     <t xml:space="preserve">  GP Equity (10%)</t>
@@ -1542,40 +1548,43 @@
     <t xml:space="preserve">KEY METRICS</t>
   </si>
   <si>
-    <t xml:space="preserve">2. In-Place Cap Rate, Day-0, reassessed tax (true going-in)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Year-1 Forward Cap Rate (includes partial-yr business plan -- used for exit-spread convention below)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exit Cap Rate (base case, Year-1-Forward basis + 50bps -- see NOI Bridge on Returns tab)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loan-to-Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binding Debt Constraint</t>
+    <t xml:space="preserve">2. In-Place Cap Rate, Day-0, reassessed tax (TRUE going-in -- anchors the exit cap below)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Year-1 Forward Cap Rate (includes partial-yr business plan -- NOT used for exit-spread convention)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit Cap Rate (base case, In-Place entry + 50bps -- see NOI Bridge on Returns tab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumed-Debt LTV at Close (fixed balance, not sized)</t>
   </si>
   <si>
     <t xml:space="preserve">Hold Period</t>
   </si>
   <si>
-    <t xml:space="preserve">RETURNS</t>
+    <t xml:space="preserve">RETURNS — BASE CASE: Scenario A, assumed debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlevered IRR (debt-agnostic)</t>
   </si>
   <si>
     <t xml:space="preserve">Levered IRR (deal-level)</t>
   </si>
   <si>
+    <t xml:space="preserve">Unlevered Equity Multiple (debt-agnostic)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Levered Equity Multiple (deal-level)</t>
   </si>
   <si>
-    <t xml:space="preserve">DEBT SCENARIO COMPARISON — neither is the base case; deal-level (pre-promote) returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B: New Debt (generic)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A: Assumed Debt</t>
+    <t xml:space="preserve">DEBT SCENARIO COMPARISON — deal-level (pre-promote) returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A: Assumed Debt (BASE CASE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B: New Debt (alternative)</t>
   </si>
   <si>
     <t xml:space="preserve">Year-0 Loan Amount</t>
@@ -1585,6 +1594,57 @@
   </si>
   <si>
     <t xml:space="preserve">Sponsor Equity Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BID PRICE — max price by target return (Scenario A, assumed debt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solved with scipy root-finding in price_solve.py (repo root), not a live in-sheet formula -- true goal-seek isn't expressible as static Excel formulas without an iterative/circular solver. Re-run that script any time Assumptions change; these are reported results, not linked cells.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs. $13.8M Asking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implied In-Place Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal IRR / LP IRR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LP clears 8% pref (LP IRR = 8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34% / 8.00%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levered IRR (deal) = 12%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.00% / 12.63%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levered IRR (deal) = 15%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.00% / 14.31%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None of the three targets hit the structural floor (~$8.78M, below which the assumed $9.45M loan would exceed Total Uses -- see price_solve.py output). All three are cleanly reachable.</t>
   </si>
   <si>
     <t xml:space="preserve">DEAL THESIS</t>
@@ -1732,7 +1792,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1822,6 +1882,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3174,17 +3238,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3194,7 +3258,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>0.015</v>
@@ -3214,262 +3278,262 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">Sensitivity!$H$53</f>
-        <v>-0.0197198671059349</v>
+        <v>0.0207257236939128</v>
       </c>
       <c r="C7" s="18" t="n">
         <f aca="false">Sensitivity!$H$54</f>
-        <v>-0.000696714812338385</v>
+        <v>0.0380287702713997</v>
       </c>
       <c r="D7" s="18" t="n">
         <f aca="false">Sensitivity!$H$55</f>
-        <v>0.0174187347421765</v>
+        <v>0.0546592689592292</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">Sensitivity!$H$56</f>
-        <v>0.0347490274956995</v>
+        <v>0.0706961380372933</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">Sensitivity!$H$57</f>
-        <v>0.0513932928613504</v>
+        <v>0.0862051762714982</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">Sensitivity!$H$58</f>
-        <v>-0.0350696976937667</v>
+        <v>0.00570795170552124</v>
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">Sensitivity!$H$59</f>
-        <v>-0.0152798550536839</v>
+        <v>0.0236030305444643</v>
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">Sensitivity!$H$60</f>
-        <v>0.00348745372831581</v>
+        <v>0.040748112613656</v>
       </c>
       <c r="E8" s="18" t="n">
         <f aca="false">Sensitivity!$H$61</f>
-        <v>0.0213782394650258</v>
+        <v>0.057235787662805</v>
       </c>
       <c r="F8" s="18" t="n">
         <f aca="false">Sensitivity!$H$62</f>
-        <v>0.0385090401930304</v>
+        <v>0.0731424511301312</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B9" s="18" t="n">
         <f aca="false">Sensitivity!$H$63</f>
-        <v>-0.0506472089709254</v>
+        <v>-0.00939030719066933</v>
       </c>
       <c r="C9" s="18" t="n">
         <f aca="false">Sensitivity!$H$64</f>
-        <v>-0.0300051925049298</v>
+        <v>0.00915434547656336</v>
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">Sensitivity!$H$65</f>
-        <v>-0.0105206468342431</v>
+        <v>0.0268598208699333</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">Sensitivity!$H$66</f>
-        <v>0.00798165321924666</v>
+        <v>0.0438353130490461</v>
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">Sensitivity!$H$67</f>
-        <v>0.0256395011673999</v>
+        <v>0.0601698948109238</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B10" s="18" t="n">
         <f aca="false">Sensitivity!$H$68</f>
-        <v>-0.0665195597307484</v>
+        <v>-0.0246197577912892</v>
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">Sensitivity!$H$69</f>
-        <v>-0.0449244972409497</v>
+        <v>-0.00535932261008771</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">Sensitivity!$H$70</f>
-        <v>-0.0246469478669002</v>
+        <v>0.0129585342243533</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">Sensitivity!$H$71</f>
-        <v>-0.0054748983935268</v>
+        <v>0.0304633438238501</v>
       </c>
       <c r="F10" s="18" t="n">
         <f aca="false">Sensitivity!$H$72</f>
-        <v>0.0127556358773992</v>
+        <v>0.0472594518201285</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B11" s="18" t="n">
         <f aca="false">Sensitivity!$H$73</f>
-        <v>-0.0827641713636604</v>
+        <v>-0.0400357786066886</v>
       </c>
       <c r="C11" s="18" t="n">
         <f aca="false">Sensitivity!$H$74</f>
-        <v>-0.0600956590375049</v>
+        <v>-0.0199827184114195</v>
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">Sensitivity!$H$75</f>
-        <v>-0.0389364830139916</v>
+        <v>-0.000993049285901724</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">Sensitivity!$H$76</f>
-        <v>-0.0190277064840361</v>
+        <v>0.0170879035460354</v>
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">Sensitivity!$H$77</f>
-        <v>-0.000172739947186342</v>
+        <v>0.0343830275807477</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B13" s="19" t="n">
         <f aca="false">Sensitivity!$I$53</f>
-        <v>0.917905724897623</v>
+        <v>1.0941069241999</v>
       </c>
       <c r="C13" s="19" t="n">
         <f aca="false">Sensitivity!$I$54</f>
-        <v>0.996991479063945</v>
+        <v>1.17846515531852</v>
       </c>
       <c r="D13" s="19" t="n">
         <f aca="false">Sensitivity!$I$55</f>
-        <v>1.07787643491636</v>
+        <v>1.26475341139092</v>
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">Sensitivity!$I$56</f>
-        <v>1.16059450704074</v>
+        <v>1.35300819105708</v>
       </c>
       <c r="F13" s="19" t="n">
         <f aca="false">Sensitivity!$I$57</f>
-        <v>1.24518009554101</v>
+        <v>1.44326651656814</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B14" s="19" t="n">
         <f aca="false">Sensitivity!$I$58</f>
-        <v>0.858744141647398</v>
+        <v>1.02509611269054</v>
       </c>
       <c r="C14" s="19" t="n">
         <f aca="false">Sensitivity!$I$59</f>
-        <v>0.936059600915709</v>
+        <v>1.10738932998074</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">Sensitivity!$I$60</f>
-        <v>1.01513033645035</v>
+        <v>1.19156133409523</v>
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false">Sensitivity!$I$61</f>
-        <v>1.09598939521125</v>
+        <v>1.27764761160555</v>
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">Sensitivity!$I$62</f>
-        <v>1.17867029688617</v>
+        <v>1.36568415777491</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">Sensitivity!$I$63</f>
-        <v>0.802724123451248</v>
+        <v>0.960030540233556</v>
       </c>
       <c r="C15" s="19" t="n">
         <f aca="false">Sensitivity!$I$64</f>
-        <v>0.878363293023598</v>
+        <v>1.04037679727306</v>
       </c>
       <c r="D15" s="19" t="n">
         <f aca="false">Sensitivity!$I$65</f>
-        <v>0.955716145945404</v>
+        <v>1.12255353221025</v>
       </c>
       <c r="E15" s="19" t="n">
         <f aca="false">Sensitivity!$I$66</f>
-        <v>1.03481490762282</v>
+        <v>1.20659527740661</v>
       </c>
       <c r="F15" s="19" t="n">
         <f aca="false">Sensitivity!$I$67</f>
-        <v>1.11569226407884</v>
+        <v>1.29253705984866</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B16" s="19" t="n">
         <f aca="false">Sensitivity!$I$68</f>
-        <v>0.749601909897505</v>
+        <v>0.898581293920261</v>
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">Sensitivity!$I$69</f>
-        <v>0.823651500921433</v>
+        <v>0.977088802210007</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">Sensitivity!$I$70</f>
-        <v>0.899375333897193</v>
+        <v>1.05738116446735</v>
       </c>
       <c r="E16" s="19" t="n">
         <f aca="false">Sensitivity!$I$71</f>
-        <v>0.976804855174519</v>
+        <v>1.13949201187841</v>
       </c>
       <c r="F16" s="19" t="n">
         <f aca="false">Sensitivity!$I$72</f>
-        <v>1.05597196023546</v>
+        <v>1.2234554569696</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B17" s="19" t="n">
         <f aca="false">Sensitivity!$I$73</f>
-        <v>0.699158323254884</v>
+        <v>0.840455034040961</v>
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">Sensitivity!$I$74</f>
-        <v>0.771698488412147</v>
+        <v>0.917223227463666</v>
       </c>
       <c r="D17" s="19" t="n">
         <f aca="false">Sensitivity!$I$75</f>
-        <v>0.845875442911018</v>
+        <v>0.995733118125832</v>
       </c>
       <c r="E17" s="19" t="n">
         <f aca="false">Sensitivity!$I$76</f>
-        <v>0.921719893327847</v>
+        <v>1.07601748477102</v>
       </c>
       <c r="F17" s="19" t="n">
         <f aca="false">Sensitivity!$I$77</f>
-        <v>0.999262984465858</v>
+        <v>1.15810957491672</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -3479,282 +3543,282 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B22" s="18" t="n">
         <f aca="false">Sensitivity!$H$78</f>
-        <v>0.0513326587933374</v>
+        <v>0.0858206247664912</v>
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">Sensitivity!$H$79</f>
-        <v>0.0398329239731552</v>
+        <v>0.0741739011687353</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">Sensitivity!$H$80</f>
-        <v>0.0283409460962099</v>
+        <v>0.0625970679695719</v>
       </c>
       <c r="E22" s="18" t="n">
         <f aca="false">Sensitivity!$H$81</f>
-        <v>0.0168351012405579</v>
+        <v>0.0510693884997548</v>
       </c>
       <c r="F22" s="18" t="n">
         <f aca="false">Sensitivity!$H$82</f>
-        <v>0.00529294230182804</v>
+        <v>0.0395700682423587</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B23" s="18" t="n">
         <f aca="false">Sensitivity!$H$83</f>
-        <v>0.0323139233398894</v>
+        <v>0.0682655889833268</v>
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">Sensitivity!$H$84</f>
-        <v>0.0195971440861583</v>
+        <v>0.0554807419250744</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">Sensitivity!$H$85</f>
-        <v>0.00685045233328115</v>
+        <v>0.0427451449313344</v>
       </c>
       <c r="E23" s="18" t="n">
         <f aca="false">Sensitivity!$H$86</f>
-        <v>-0.0059563132883712</v>
+        <v>0.0300313567939133</v>
       </c>
       <c r="F23" s="18" t="n">
         <f aca="false">Sensitivity!$H$87</f>
-        <v>-0.0188552039694911</v>
+        <v>0.0173113606685587</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B24" s="18" t="n">
         <f aca="false">Sensitivity!$H$88</f>
-        <v>0.0140435461099893</v>
+        <v>0.0514789199168022</v>
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">Sensitivity!$H$89</f>
-        <v>3.12004312866405E-005</v>
+        <v>0.0374984454529282</v>
       </c>
       <c r="D24" s="18" t="n">
         <f aca="false">Sensitivity!$H$90</f>
-        <v>-0.0140635018559876</v>
+        <v>0.0235369032465124</v>
       </c>
       <c r="E24" s="18" t="n">
         <f aca="false">Sensitivity!$H$91</f>
-        <v>-0.0282827608031383</v>
+        <v>0.00955791635878041</v>
       </c>
       <c r="F24" s="18" t="n">
         <f aca="false">Sensitivity!$H$92</f>
-        <v>-0.0426726006677387</v>
+        <v>-0.00447642654382599</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B25" s="18" t="n">
         <f aca="false">Sensitivity!$H$93</f>
-        <v>-0.00363942093402338</v>
+        <v>0.0353124347506857</v>
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">Sensitivity!$H$94</f>
-        <v>-0.019035295064772</v>
+        <v>0.0200731311749729</v>
       </c>
       <c r="D25" s="18" t="n">
         <f aca="false">Sensitivity!$H$95</f>
-        <v>-0.034584761370627</v>
+        <v>0.00481041652107196</v>
       </c>
       <c r="E25" s="18" t="n">
         <f aca="false">Sensitivity!$H$96</f>
-        <v>-0.0503470669631719</v>
+        <v>-0.0105240473336652</v>
       </c>
       <c r="F25" s="18" t="n">
         <f aca="false">Sensitivity!$H$97</f>
-        <v>-0.0663887020694382</v>
+        <v>-0.0259818133351271</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B26" s="18" t="n">
         <f aca="false">Sensitivity!$H$98</f>
-        <v>-0.0208748819342042</v>
+        <v>0.0196395922123318</v>
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">Sensitivity!$H$99</f>
-        <v>-0.0377537171102106</v>
+        <v>0.00307146201556129</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">Sensitivity!$H$100</f>
-        <v>-0.0548813739420978</v>
+        <v>-0.0135773699672616</v>
       </c>
       <c r="E26" s="18" t="n">
         <f aca="false">Sensitivity!$H$101</f>
-        <v>-0.0723413678414331</v>
+        <v>-0.0303713313778217</v>
       </c>
       <c r="F26" s="18" t="n">
         <f aca="false">Sensitivity!$H$102</f>
-        <v>-0.0902304161369946</v>
+        <v>-0.0473809153121889</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B28" s="19" t="n">
         <f aca="false">Sensitivity!$I$78</f>
-        <v>1.23560283764524</v>
+        <v>1.42490137295093</v>
       </c>
       <c r="C28" s="19" t="n">
         <f aca="false">Sensitivity!$I$79</f>
-        <v>1.17824314145235</v>
+        <v>1.35797799617879</v>
       </c>
       <c r="D28" s="19" t="n">
         <f aca="false">Sensitivity!$I$80</f>
-        <v>1.12363937367189</v>
+        <v>1.29451773080338</v>
       </c>
       <c r="E28" s="19" t="n">
         <f aca="false">Sensitivity!$I$81</f>
-        <v>1.07159757506129</v>
+        <v>1.2342585459673</v>
       </c>
       <c r="F28" s="19" t="n">
         <f aca="false">Sensitivity!$I$82</f>
-        <v>1.02194157003375</v>
+        <v>1.17696419536563</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B29" s="19" t="n">
         <f aca="false">Sensitivity!$I$83</f>
-        <v>1.14651310785224</v>
+        <v>1.33462180533239</v>
       </c>
       <c r="C29" s="19" t="n">
         <f aca="false">Sensitivity!$I$84</f>
-        <v>1.08642948932094</v>
+        <v>1.26452791111696</v>
       </c>
       <c r="D29" s="19" t="n">
         <f aca="false">Sensitivity!$I$85</f>
-        <v>1.02938493986569</v>
+        <v>1.19825172884989</v>
       </c>
       <c r="E29" s="19" t="n">
         <f aca="false">Sensitivity!$I$86</f>
-        <v>0.975154569840683</v>
+        <v>1.13548962586823</v>
       </c>
       <c r="F29" s="19" t="n">
         <f aca="false">Sensitivity!$I$87</f>
-        <v>0.923535144418525</v>
+        <v>1.07596933622137</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B30" s="19" t="n">
         <f aca="false">Sensitivity!$I$88</f>
-        <v>1.06285892074421</v>
+        <v>1.24966832270182</v>
       </c>
       <c r="C30" s="19" t="n">
         <f aca="false">Sensitivity!$I$89</f>
-        <v>1.00013551120101</v>
+        <v>1.17650271158383</v>
       </c>
       <c r="D30" s="19" t="n">
         <f aca="false">Sensitivity!$I$90</f>
-        <v>0.940742804804476</v>
+        <v>1.10751986284699</v>
       </c>
       <c r="E30" s="19" t="n">
         <f aca="false">Sensitivity!$I$91</f>
-        <v>0.884422365534283</v>
+        <v>1.0423710613633</v>
       </c>
       <c r="F30" s="19" t="n">
         <f aca="false">Sensitivity!$I$92</f>
-        <v>0.830941820052078</v>
+        <v>0.980745306890108</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B31" s="19" t="n">
         <f aca="false">Sensitivity!$I$93</f>
-        <v>0.983929739567733</v>
+        <v>1.1693446966686</v>
       </c>
       <c r="C31" s="19" t="n">
         <f aca="false">Sensitivity!$I$94</f>
-        <v>0.918650794314117</v>
+        <v>1.09320627925641</v>
       </c>
       <c r="D31" s="19" t="n">
         <f aca="false">Sensitivity!$I$95</f>
-        <v>0.857001936968397</v>
+        <v>1.02162518377028</v>
       </c>
       <c r="E31" s="19" t="n">
         <f aca="false">Sensitivity!$I$96</f>
-        <v>0.798688561298899</v>
+        <v>0.954204127177581</v>
       </c>
       <c r="F31" s="19" t="n">
         <f aca="false">Sensitivity!$I$97</f>
-        <v>0.743447100444841</v>
+        <v>0.890590699860086</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B32" s="19" t="n">
         <f aca="false">Sensitivity!$I$98</f>
-        <v>0.909133698918872</v>
+        <v>1.09307098045915</v>
       </c>
       <c r="C32" s="19" t="n">
         <f aca="false">Sensitivity!$I$99</f>
-        <v>0.841383518548304</v>
+        <v>1.01405868580693</v>
       </c>
       <c r="D32" s="19" t="n">
         <f aca="false">Sensitivity!$I$100</f>
-        <v>0.777569829929285</v>
+        <v>0.939986856141731</v>
       </c>
       <c r="E32" s="19" t="n">
         <f aca="false">Sensitivity!$I$101</f>
-        <v>0.71735923553384</v>
+        <v>0.870406164562253</v>
       </c>
       <c r="F32" s="19" t="n">
         <f aca="false">Sensitivity!$I$102</f>
-        <v>0.660454953193025</v>
+        <v>0.804920168285205</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -3764,282 +3828,282 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="E36" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>371</v>
-      </c>
       <c r="F36" s="14" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B37" s="18" t="n">
         <f aca="false">Sensitivity!$H$103</f>
-        <v>-0.129529338432886</v>
+        <v>-0.0771176338037826</v>
       </c>
       <c r="C37" s="18" t="n">
         <f aca="false">Sensitivity!$H$104</f>
-        <v>-0.131367253706609</v>
+        <v>-0.0790303347678829</v>
       </c>
       <c r="D37" s="18" t="n">
         <f aca="false">Sensitivity!$H$105</f>
-        <v>-0.13318343348128</v>
+        <v>-0.0809206289776866</v>
       </c>
       <c r="E37" s="18" t="n">
         <f aca="false">Sensitivity!$H$106</f>
-        <v>-0.13497833608039</v>
+        <v>-0.0827889856239902</v>
       </c>
       <c r="F37" s="18" t="n">
         <f aca="false">Sensitivity!$H$107</f>
-        <v>-0.136752406039614</v>
+        <v>-0.0846358598627693</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B38" s="18" t="n">
         <f aca="false">Sensitivity!$H$108</f>
-        <v>-0.112790008081192</v>
+        <v>-0.062955717752434</v>
       </c>
       <c r="C38" s="18" t="n">
         <f aca="false">Sensitivity!$H$109</f>
-        <v>-0.114664077662226</v>
+        <v>-0.0649006747100014</v>
       </c>
       <c r="D38" s="18" t="n">
         <f aca="false">Sensitivity!$H$110</f>
-        <v>-0.116515979431841</v>
+        <v>-0.0668228295496783</v>
       </c>
       <c r="E38" s="18" t="n">
         <f aca="false">Sensitivity!$H$111</f>
-        <v>-0.118346180892634</v>
+        <v>-0.068722660004182</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">Sensitivity!$H$112</f>
-        <v>-0.12015513548199</v>
+        <v>-0.0706006295096657</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B39" s="18" t="n">
         <f aca="false">Sensitivity!$H$113</f>
-        <v>-0.0971144954430443</v>
+        <v>-0.0495048935188046</v>
       </c>
       <c r="C39" s="18" t="n">
         <f aca="false">Sensitivity!$H$114</f>
-        <v>-0.0990228799637324</v>
+        <v>-0.0514807762452103</v>
       </c>
       <c r="D39" s="18" t="n">
         <f aca="false">Sensitivity!$H$115</f>
-        <v>-0.100908683338398</v>
+        <v>-0.053433475853638</v>
       </c>
       <c r="E39" s="18" t="n">
         <f aca="false">Sensitivity!$H$116</f>
-        <v>-0.102772381894187</v>
+        <v>-0.055363478339491</v>
       </c>
       <c r="F39" s="18" t="n">
         <f aca="false">Sensitivity!$H$117</f>
-        <v>-0.104614437625108</v>
+        <v>-0.05727125514765</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B40" s="18" t="n">
         <f aca="false">Sensitivity!$H$118</f>
-        <v>-0.0823536615596951</v>
+        <v>-0.0366847941525038</v>
       </c>
       <c r="C40" s="18" t="n">
         <f aca="false">Sensitivity!$H$119</f>
-        <v>-0.0842947647910973</v>
+        <v>-0.0386904189301734</v>
       </c>
       <c r="D40" s="18" t="n">
         <f aca="false">Sensitivity!$H$120</f>
-        <v>-0.0862128901036781</v>
+        <v>-0.0406724923911844</v>
       </c>
       <c r="E40" s="18" t="n">
         <f aca="false">Sensitivity!$H$121</f>
-        <v>-0.0881085223381404</v>
+        <v>-0.0426315085444882</v>
       </c>
       <c r="F40" s="18" t="n">
         <f aca="false">Sensitivity!$H$122</f>
-        <v>-0.0899821317424673</v>
+        <v>-0.0445679466015034</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B41" s="18" t="n">
         <f aca="false">Sensitivity!$H$123</f>
-        <v>-0.0683887101893623</v>
+        <v>-0.0244284060339821</v>
       </c>
       <c r="C41" s="18" t="n">
         <f aca="false">Sensitivity!$H$124</f>
-        <v>-0.0703611319179342</v>
+        <v>-0.026462711775903</v>
       </c>
       <c r="D41" s="18" t="n">
         <f aca="false">Sensitivity!$H$125</f>
-        <v>-0.0723101935522196</v>
+        <v>-0.0284731094931717</v>
       </c>
       <c r="E41" s="18" t="n">
         <f aca="false">Sensitivity!$H$126</f>
-        <v>-0.0742363881712281</v>
+        <v>-0.0304601009844406</v>
       </c>
       <c r="F41" s="18" t="n">
         <f aca="false">Sensitivity!$H$127</f>
-        <v>-0.0761401940091858</v>
+        <v>-0.0324241730100852</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B43" s="19" t="n">
         <f aca="false">Sensitivity!$I$103</f>
-        <v>0.563914225426456</v>
+        <v>0.709874371731879</v>
       </c>
       <c r="C43" s="19" t="n">
         <f aca="false">Sensitivity!$I$104</f>
-        <v>0.558860243389553</v>
+        <v>0.703512247562237</v>
       </c>
       <c r="D43" s="19" t="n">
         <f aca="false">Sensitivity!$I$105</f>
-        <v>0.553896047509748</v>
+        <v>0.697263149255369</v>
       </c>
       <c r="E43" s="19" t="n">
         <f aca="false">Sensitivity!$I$106</f>
-        <v>0.549019266218657</v>
+        <v>0.691124091400482</v>
       </c>
       <c r="F43" s="19" t="n">
         <f aca="false">Sensitivity!$I$107</f>
-        <v>0.544227610740903</v>
+        <v>0.685092192809427</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B44" s="19" t="n">
         <f aca="false">Sensitivity!$I$108</f>
-        <v>0.608826464238361</v>
+        <v>0.757236205760052</v>
       </c>
       <c r="C44" s="19" t="n">
         <f aca="false">Sensitivity!$I$109</f>
-        <v>0.603369964162441</v>
+        <v>0.75044960948522</v>
       </c>
       <c r="D44" s="19" t="n">
         <f aca="false">Sensitivity!$I$110</f>
-        <v>0.598010401149106</v>
+        <v>0.743783580002047</v>
       </c>
       <c r="E44" s="19" t="n">
         <f aca="false">Sensitivity!$I$111</f>
-        <v>0.592745214749396</v>
+        <v>0.737234932717268</v>
       </c>
       <c r="F44" s="19" t="n">
         <f aca="false">Sensitivity!$I$112</f>
-        <v>0.587571933901297</v>
+        <v>0.730800594213855</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B45" s="19" t="n">
         <f aca="false">Sensitivity!$I$113</f>
-        <v>0.653738703050266</v>
+        <v>0.804598039788225</v>
       </c>
       <c r="C45" s="19" t="n">
         <f aca="false">Sensitivity!$I$114</f>
-        <v>0.647879684935329</v>
+        <v>0.797386971408204</v>
       </c>
       <c r="D45" s="19" t="n">
         <f aca="false">Sensitivity!$I$115</f>
-        <v>0.642124754788466</v>
+        <v>0.790304010748724</v>
       </c>
       <c r="E45" s="19" t="n">
         <f aca="false">Sensitivity!$I$116</f>
-        <v>0.636471163280136</v>
+        <v>0.783345774034054</v>
       </c>
       <c r="F45" s="19" t="n">
         <f aca="false">Sensitivity!$I$117</f>
-        <v>0.630916257061692</v>
+        <v>0.776508995618284</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B46" s="19" t="n">
         <f aca="false">Sensitivity!$I$118</f>
-        <v>0.69865094186217</v>
+        <v>0.851959873816398</v>
       </c>
       <c r="C46" s="19" t="n">
         <f aca="false">Sensitivity!$I$119</f>
-        <v>0.692389405708216</v>
+        <v>0.844324333331187</v>
       </c>
       <c r="D46" s="19" t="n">
         <f aca="false">Sensitivity!$I$120</f>
-        <v>0.686239108427824</v>
+        <v>0.836824441495402</v>
       </c>
       <c r="E46" s="19" t="n">
         <f aca="false">Sensitivity!$I$121</f>
-        <v>0.680197111810875</v>
+        <v>0.829456615350839</v>
       </c>
       <c r="F46" s="19" t="n">
         <f aca="false">Sensitivity!$I$122</f>
-        <v>0.674260580222086</v>
+        <v>0.822217397022712</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B47" s="19" t="n">
         <f aca="false">Sensitivity!$I$123</f>
-        <v>0.743563180674075</v>
+        <v>0.899321707844571</v>
       </c>
       <c r="C47" s="19" t="n">
         <f aca="false">Sensitivity!$I$124</f>
-        <v>0.736899126481104</v>
+        <v>0.891261695254171</v>
       </c>
       <c r="D47" s="19" t="n">
         <f aca="false">Sensitivity!$I$125</f>
-        <v>0.730353462067183</v>
+        <v>0.883344872242079</v>
       </c>
       <c r="E47" s="19" t="n">
         <f aca="false">Sensitivity!$I$126</f>
-        <v>0.723923060341614</v>
+        <v>0.875567456667625</v>
       </c>
       <c r="F47" s="19" t="n">
         <f aca="false">Sensitivity!$I$127</f>
-        <v>0.71760490338248</v>
+        <v>0.867925798427141</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -4052,7 +4116,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>265</v>
@@ -4073,15 +4137,15 @@
         <v>270</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B53" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4105,20 +4169,20 @@
       </c>
       <c r="G53" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.015)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.015)^6)/((Returns!$B$33+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>3665580.6435196</v>
+        <v>4639627.92131058</v>
       </c>
       <c r="H53" s="18" t="n">
         <f aca="false">IFERROR(IRR(B53:G53),"N/A")</f>
-        <v>-0.0197198671059349</v>
+        <v>0.0207257236939128</v>
       </c>
       <c r="I53" s="19" t="n">
         <f aca="false">SUM(C53:G53)/(Capital!$B$12)</f>
-        <v>0.917905724897623</v>
+        <v>1.0941069241999</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B54" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4142,20 +4206,20 @@
       </c>
       <c r="G54" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.02)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.02)^6)/((Returns!$B$33+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>4051116.54318206</v>
+        <v>5054310.28446441</v>
       </c>
       <c r="H54" s="18" t="n">
         <f aca="false">IFERROR(IRR(B54:G54),"N/A")</f>
-        <v>-0.000696714812338385</v>
+        <v>0.0380287702713997</v>
       </c>
       <c r="I54" s="19" t="n">
         <f aca="false">SUM(C54:G54)/(Capital!$B$12)</f>
-        <v>0.996991479063945</v>
+        <v>1.17846515531852</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B55" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4179,20 +4243,20 @@
       </c>
       <c r="G55" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.025)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.025)^6)/((Returns!$B$33+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>4446084.57365105</v>
+        <v>5479147.97468146</v>
       </c>
       <c r="H55" s="18" t="n">
         <f aca="false">IFERROR(IRR(B55:G55),"N/A")</f>
-        <v>0.0174187347421765</v>
+        <v>0.0546592689592292</v>
       </c>
       <c r="I55" s="19" t="n">
         <f aca="false">SUM(C55:G55)/(Capital!$B$12)</f>
-        <v>1.07787643491636</v>
+        <v>1.26475341139092</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B56" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4216,20 +4280,20 @@
       </c>
       <c r="G56" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.03)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.03)^6)/((Returns!$B$33+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>4850668.40745622</v>
+        <v>5914338.94924589</v>
       </c>
       <c r="H56" s="18" t="n">
         <f aca="false">IFERROR(IRR(B56:G56),"N/A")</f>
-        <v>0.0347490274956995</v>
+        <v>0.0706961380372933</v>
       </c>
       <c r="I56" s="19" t="n">
         <f aca="false">SUM(C56:G56)/(Capital!$B$12)</f>
-        <v>1.16059450704074</v>
+        <v>1.35300819105708</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B57" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4253,20 +4317,20 @@
       </c>
       <c r="G57" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.035)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.035)^6)/((Returns!$B$33+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>5265054.38612528</v>
+        <v>6360084.04502009</v>
       </c>
       <c r="H57" s="18" t="n">
         <f aca="false">IFERROR(IRR(B57:G57),"N/A")</f>
-        <v>0.0513932928613504</v>
+        <v>0.0862051762714982</v>
       </c>
       <c r="I57" s="19" t="n">
         <f aca="false">SUM(C57:G57)/(Capital!$B$12)</f>
-        <v>1.24518009554101</v>
+        <v>1.44326651656814</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B58" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4290,20 +4354,20 @@
       </c>
       <c r="G58" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.015)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.015)^6)/((Returns!$B$33+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>3338533.04484902</v>
+        <v>4258133.39485436</v>
       </c>
       <c r="H58" s="18" t="n">
         <f aca="false">IFERROR(IRR(B58:G58),"N/A")</f>
-        <v>-0.0350696976937667</v>
+        <v>0.00570795170552124</v>
       </c>
       <c r="I58" s="19" t="n">
         <f aca="false">SUM(C58:G58)/(Capital!$B$12)</f>
-        <v>0.858744141647398</v>
+        <v>1.02509611269054</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B59" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4327,20 +4391,20 @@
       </c>
       <c r="G59" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.02)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.02)^6)/((Returns!$B$33+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>3714282.68350349</v>
+        <v>4661400.27896416</v>
       </c>
       <c r="H59" s="18" t="n">
         <f aca="false">IFERROR(IRR(B59:G59),"N/A")</f>
-        <v>-0.0152798550536839</v>
+        <v>0.0236030305444643</v>
       </c>
       <c r="I59" s="19" t="n">
         <f aca="false">SUM(C59:G59)/(Capital!$B$12)</f>
-        <v>0.936059600915709</v>
+        <v>1.10738932998074</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B60" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4364,20 +4428,20 @@
       </c>
       <c r="G60" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.025)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.025)^6)/((Returns!$B$33+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>4099221.63148701</v>
+        <v>5074539.24370781</v>
       </c>
       <c r="H60" s="18" t="n">
         <f aca="false">IFERROR(IRR(B60:G60),"N/A")</f>
-        <v>0.00348745372831581</v>
+        <v>0.040748112613656</v>
       </c>
       <c r="I60" s="19" t="n">
         <f aca="false">SUM(C60:G60)/(Capital!$B$12)</f>
-        <v>1.01513033645035</v>
+        <v>1.19156133409523</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B61" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4401,20 +4465,20 @@
       </c>
       <c r="G61" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.03)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.03)^6)/((Returns!$B$33+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>4493528.76505829</v>
+        <v>5497742.65161468</v>
       </c>
       <c r="H61" s="18" t="n">
         <f aca="false">IFERROR(IRR(B61:G61),"N/A")</f>
-        <v>0.0213782394650258</v>
+        <v>0.057235787662805</v>
       </c>
       <c r="I61" s="19" t="n">
         <f aca="false">SUM(C61:G61)/(Capital!$B$12)</f>
-        <v>1.09598939521125</v>
+        <v>1.27764761160555</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B62" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4438,20 +4502,20 @@
       </c>
       <c r="G62" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.035)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.035)^6)/((Returns!$B$33+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>4897385.55876939</v>
+        <v>5931205.66231674</v>
       </c>
       <c r="H62" s="18" t="n">
         <f aca="false">IFERROR(IRR(B62:G62),"N/A")</f>
-        <v>0.0385090401930304</v>
+        <v>0.0731424511301312</v>
       </c>
       <c r="I62" s="19" t="n">
         <f aca="false">SUM(C62:G62)/(Capital!$B$12)</f>
-        <v>1.17867029688617</v>
+        <v>1.36568415777491</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B63" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4475,20 +4539,20 @@
       </c>
       <c r="G63" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.015)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.015)^6)/((Returns!$B$33+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>3028852.14345998</v>
+        <v>3898448.30768925</v>
       </c>
       <c r="H63" s="18" t="n">
         <f aca="false">IFERROR(IRR(B63:G63),"N/A")</f>
-        <v>-0.0506472089709254</v>
+        <v>-0.00939030719066933</v>
       </c>
       <c r="I63" s="19" t="n">
         <f aca="false">SUM(C63:G63)/(Capital!$B$12)</f>
-        <v>0.802724123451248</v>
+        <v>0.960030540233556</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B64" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4512,20 +4576,20 @@
       </c>
       <c r="G64" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.02)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.02)^6)/((Returns!$B$33+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>3395335.18562358</v>
+        <v>4290952.31765477</v>
       </c>
       <c r="H64" s="18" t="n">
         <f aca="false">IFERROR(IRR(B64:G64),"N/A")</f>
-        <v>-0.0300051925049298</v>
+        <v>0.00915434547656336</v>
       </c>
       <c r="I64" s="19" t="n">
         <f aca="false">SUM(C64:G64)/(Capital!$B$12)</f>
-        <v>0.878363293023598</v>
+        <v>1.04037679727306</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B65" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4549,20 +4613,20 @@
       </c>
       <c r="G65" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.025)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.025)^6)/((Returns!$B$33+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>3770777.60980803</v>
+        <v>4693061.35457557</v>
       </c>
       <c r="H65" s="18" t="n">
         <f aca="false">IFERROR(IRR(B65:G65),"N/A")</f>
-        <v>-0.0105206468342431</v>
+        <v>0.0268598208699333</v>
       </c>
       <c r="I65" s="19" t="n">
         <f aca="false">SUM(C65:G65)/(Capital!$B$12)</f>
-        <v>0.955716145945404</v>
+        <v>1.12255353221025</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B66" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4586,20 +4650,20 @@
       </c>
       <c r="G66" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.03)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.03)^6)/((Returns!$B$33+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>4155353.75068996</v>
+        <v>5104962.50606955</v>
       </c>
       <c r="H66" s="18" t="n">
         <f aca="false">IFERROR(IRR(B66:G66),"N/A")</f>
-        <v>0.00798165321924666</v>
+        <v>0.0438353130490461</v>
       </c>
       <c r="I66" s="19" t="n">
         <f aca="false">SUM(C66:G66)/(Capital!$B$12)</f>
-        <v>1.03481490762282</v>
+        <v>1.20659527740661</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B67" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4623,20 +4687,20 @@
       </c>
       <c r="G67" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.035)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.035)^6)/((Returns!$B$33+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>4549240.47428916</v>
+        <v>5526845.57909655</v>
       </c>
       <c r="H67" s="18" t="n">
         <f aca="false">IFERROR(IRR(B67:G67),"N/A")</f>
-        <v>0.0256395011673999</v>
+        <v>0.0601698948109238</v>
       </c>
       <c r="I67" s="19" t="n">
         <f aca="false">SUM(C67:G67)/(Capital!$B$12)</f>
-        <v>1.11569226407884</v>
+        <v>1.29253705984866</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B68" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4660,20 +4724,20 @@
       </c>
       <c r="G68" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.015)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.015)^6)/((Returns!$B$33+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2735190.42204635</v>
+        <v>3558754.4160995</v>
       </c>
       <c r="H68" s="18" t="n">
         <f aca="false">IFERROR(IRR(B68:G68),"N/A")</f>
-        <v>-0.0665195597307484</v>
+        <v>-0.0246197577912892</v>
       </c>
       <c r="I68" s="19" t="n">
         <f aca="false">SUM(C68:G68)/(Capital!$B$12)</f>
-        <v>0.749601909897505</v>
+        <v>0.898581293920261</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B69" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4697,20 +4761,20 @@
       </c>
       <c r="G69" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.02)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.02)^6)/((Returns!$B$33+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>3092886.21041113</v>
+        <v>3941093.74942641</v>
       </c>
       <c r="H69" s="18" t="n">
         <f aca="false">IFERROR(IRR(B69:G69),"N/A")</f>
-        <v>-0.0449244972409497</v>
+        <v>-0.00535932261008771</v>
       </c>
       <c r="I69" s="19" t="n">
         <f aca="false">SUM(C69:G69)/(Capital!$B$12)</f>
-        <v>0.823651500921433</v>
+        <v>0.977088802210007</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B70" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4734,20 +4798,20 @@
       </c>
       <c r="G70" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.025)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.025)^6)/((Returns!$B$33+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>3459323.34717303</v>
+        <v>4332785.89879809</v>
       </c>
       <c r="H70" s="18" t="n">
         <f aca="false">IFERROR(IRR(B70:G70),"N/A")</f>
-        <v>-0.0246469478669002</v>
+        <v>0.0129585342243533</v>
       </c>
       <c r="I70" s="19" t="n">
         <f aca="false">SUM(C70:G70)/(Capital!$B$12)</f>
-        <v>0.899375333897193</v>
+        <v>1.05738116446735</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B71" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4771,20 +4835,20 @@
       </c>
       <c r="G71" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.03)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.03)^6)/((Returns!$B$33+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>3834671.86035367</v>
+        <v>4734012.97009904</v>
       </c>
       <c r="H71" s="18" t="n">
         <f aca="false">IFERROR(IRR(B71:G71),"N/A")</f>
-        <v>-0.0054748983935268</v>
+        <v>0.0304633438238501</v>
       </c>
       <c r="I71" s="19" t="n">
         <f aca="false">SUM(C71:G71)/(Capital!$B$12)</f>
-        <v>0.976804855174519</v>
+        <v>1.13949201187841</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B72" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4808,20 +4872,20 @@
       </c>
       <c r="G72" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.035)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.035)^6)/((Returns!$B$33+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>4219104.24583081</v>
+        <v>5144959.71511697</v>
       </c>
       <c r="H72" s="18" t="n">
         <f aca="false">IFERROR(IRR(B72:G72),"N/A")</f>
-        <v>0.0127556358773992</v>
+        <v>0.0472594518201285</v>
       </c>
       <c r="I72" s="19" t="n">
         <f aca="false">SUM(C72:G72)/(Capital!$B$12)</f>
-        <v>1.05597196023546</v>
+        <v>1.2234554569696</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B73" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4845,20 +4909,20 @@
       </c>
       <c r="G73" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.015)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.015)^6)/((Returns!$B$33+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2456336.25734247</v>
+        <v>3237430.12643634</v>
       </c>
       <c r="H73" s="18" t="n">
         <f aca="false">IFERROR(IRR(B73:G73),"N/A")</f>
-        <v>-0.0827641713636604</v>
+        <v>-0.0400357786066886</v>
       </c>
       <c r="I73" s="19" t="n">
         <f aca="false">SUM(C73:G73)/(Capital!$B$12)</f>
-        <v>0.699158323254884</v>
+        <v>0.840455034040961</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B74" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4882,20 +4946,20 @@
       </c>
       <c r="G74" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.02)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.02)^6)/((Returns!$B$33+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2805687.87913929</v>
+        <v>3610154.45760565</v>
       </c>
       <c r="H74" s="18" t="n">
         <f aca="false">IFERROR(IRR(B74:G74),"N/A")</f>
-        <v>-0.0600956590375049</v>
+        <v>-0.0199827184114195</v>
       </c>
       <c r="I74" s="19" t="n">
         <f aca="false">SUM(C74:G74)/(Capital!$B$12)</f>
-        <v>0.771698488412147</v>
+        <v>0.917223227463666</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B75" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4919,20 +4983,20 @@
       </c>
       <c r="G75" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.025)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.025)^6)/((Returns!$B$33+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>3163573.80980582</v>
+        <v>3991993.03270032</v>
       </c>
       <c r="H75" s="18" t="n">
         <f aca="false">IFERROR(IRR(B75:G75),"N/A")</f>
-        <v>-0.0389364830139916</v>
+        <v>-0.000993049285901724</v>
       </c>
       <c r="I75" s="19" t="n">
         <f aca="false">SUM(C75:G75)/(Capital!$B$12)</f>
-        <v>0.845875442911018</v>
+        <v>0.995733118125832</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B76" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4956,20 +5020,20 @@
       </c>
       <c r="G76" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.03)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.03)^6)/((Returns!$B$33+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>3530159.98786679</v>
+        <v>4383123.2452683</v>
       </c>
       <c r="H76" s="18" t="n">
         <f aca="false">IFERROR(IRR(B76:G76),"N/A")</f>
-        <v>-0.0190277064840361</v>
+        <v>0.0170879035460354</v>
       </c>
       <c r="I76" s="19" t="n">
         <f aca="false">SUM(C76:G76)/(Capital!$B$12)</f>
-        <v>0.921719893327847</v>
+        <v>1.07601748477102</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B77" s="16" t="n">
         <f aca="false">-(Capital!$B$12)</f>
@@ -4993,20 +5057,20 @@
       </c>
       <c r="G77" s="16" t="n">
         <f aca="false">(('Operating Model'!$B$43*(1+0.035)^5)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((('Operating Model'!$B$43*(1+0.035)^6)/((Returns!$B$33+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>3905614.75941739</v>
+        <v>4783725.06529335</v>
       </c>
       <c r="H77" s="18" t="n">
         <f aca="false">IFERROR(IRR(B77:G77),"N/A")</f>
-        <v>-0.000172739947186342</v>
+        <v>0.0343830275807477</v>
       </c>
       <c r="I77" s="19" t="n">
         <f aca="false">SUM(C77:G77)/(Capital!$B$12)</f>
-        <v>0.999262984465858</v>
+        <v>1.15810957491672</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B78" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+-0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))</f>
@@ -5029,21 +5093,21 @@
         <v>458503.878902682</v>
       </c>
       <c r="G78" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.1)))+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89),1,3,0))))</f>
-        <v>4397401.62685288</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.1)))+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89),1,3,0))))</f>
+        <v>5348501.82973065</v>
       </c>
       <c r="H78" s="18" t="n">
         <f aca="false">IFERROR(IRR(B78:G78),"N/A")</f>
-        <v>0.0513326587933374</v>
+        <v>0.0858206247664912</v>
       </c>
       <c r="I78" s="19" t="n">
         <f aca="false">SUM(C78:G78)/((((Assumptions!$C$7*(1+-0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))</f>
-        <v>1.23560283764524</v>
+        <v>1.42490137295093</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B79" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+-0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))</f>
@@ -5066,21 +5130,21 @@
         <v>458503.878902682</v>
       </c>
       <c r="G79" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.1)))+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89),1,3,0))))</f>
-        <v>4109207.01088308</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.1)))+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89),1,3,0))))</f>
+        <v>5012256.03087934</v>
       </c>
       <c r="H79" s="18" t="n">
         <f aca="false">IFERROR(IRR(B79:G79),"N/A")</f>
-        <v>0.0398329239731552</v>
+        <v>0.0741739011687353</v>
       </c>
       <c r="I79" s="19" t="n">
         <f aca="false">SUM(C79:G79)/((((Assumptions!$C$7*(1+-0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))</f>
-        <v>1.17824314145235</v>
+        <v>1.35797799617879</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B80" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+-0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))</f>
@@ -5103,21 +5167,21 @@
         <v>458503.878902682</v>
       </c>
       <c r="G80" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.1)))+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3834859.11627301</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.1)))+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89),1,3,0))))</f>
+        <v>4693410.08114304</v>
       </c>
       <c r="H80" s="18" t="n">
         <f aca="false">IFERROR(IRR(B80:G80),"N/A")</f>
-        <v>0.0283409460962099</v>
+        <v>0.0625970679695719</v>
       </c>
       <c r="I80" s="19" t="n">
         <f aca="false">SUM(C80:G80)/((((Assumptions!$C$7*(1+-0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))</f>
-        <v>1.12363937367189</v>
+        <v>1.29451773080338</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B81" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+-0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))</f>
@@ -5140,21 +5204,21 @@
         <v>458503.878902682</v>
       </c>
       <c r="G81" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.1)))+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3573383.42584184</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.1)))+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89),1,3,0))))</f>
+        <v>4390647.44840374</v>
       </c>
       <c r="H81" s="18" t="n">
         <f aca="false">IFERROR(IRR(B81:G81),"N/A")</f>
-        <v>0.0168351012405579</v>
+        <v>0.0510693884997548</v>
       </c>
       <c r="I81" s="19" t="n">
         <f aca="false">SUM(C81:G81)/((((Assumptions!$C$7*(1+-0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))</f>
-        <v>1.07159757506129</v>
+        <v>1.2342585459673</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B82" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+-0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))</f>
@@ -5177,21 +5241,21 @@
         <v>458503.878902682</v>
       </c>
       <c r="G82" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.1)))+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3323894.77354179</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.1)))+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89),1,3,0))))</f>
+        <v>4102781.15090177</v>
       </c>
       <c r="H82" s="18" t="n">
         <f aca="false">IFERROR(IRR(B82:G82),"N/A")</f>
-        <v>0.00529294230182804</v>
+        <v>0.0395700682423587</v>
       </c>
       <c r="I82" s="19" t="n">
         <f aca="false">SUM(C82:G82)/((((Assumptions!$C$7*(1+-0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.1))*Assumptions!$C$89)))</f>
-        <v>1.02194157003375</v>
+        <v>1.17696419536563</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B83" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+-0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))</f>
@@ -5214,21 +5278,21 @@
         <v>409282.362942262</v>
       </c>
       <c r="G83" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.05)))+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89),1,3,0))))</f>
-        <v>4423914.24957676</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.05)))+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89),1,3,0))))</f>
+        <v>5416411.47813452</v>
       </c>
       <c r="H83" s="18" t="n">
         <f aca="false">IFERROR(IRR(B83:G83),"N/A")</f>
-        <v>0.0323139233398894</v>
+        <v>0.0682655889833268</v>
       </c>
       <c r="I83" s="19" t="n">
         <f aca="false">SUM(C83:G83)/((((Assumptions!$C$7*(1+-0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))</f>
-        <v>1.14651310785224</v>
+        <v>1.33462180533239</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B84" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+-0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))</f>
@@ -5251,21 +5315,21 @@
         <v>409282.362942262</v>
       </c>
       <c r="G84" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.05)))+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89),1,3,0))))</f>
-        <v>4106901.6623181</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.05)))+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89),1,3,0))))</f>
+        <v>5046582.77441401</v>
       </c>
       <c r="H84" s="18" t="n">
         <f aca="false">IFERROR(IRR(B84:G84),"N/A")</f>
-        <v>0.0195971440861583</v>
+        <v>0.0554807419250744</v>
       </c>
       <c r="I84" s="19" t="n">
         <f aca="false">SUM(C84:G84)/((((Assumptions!$C$7*(1+-0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))</f>
-        <v>1.08642948932094</v>
+        <v>1.26452791111696</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B85" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+-0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))</f>
@@ -5288,21 +5352,21 @@
         <v>409282.362942262</v>
       </c>
       <c r="G85" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.05)))+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3805923.78092777</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.05)))+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89),1,3,0))))</f>
+        <v>4696897.04429836</v>
       </c>
       <c r="H85" s="18" t="n">
         <f aca="false">IFERROR(IRR(B85:G85),"N/A")</f>
-        <v>0.00685045233328115</v>
+        <v>0.0427451449313344</v>
       </c>
       <c r="I85" s="19" t="n">
         <f aca="false">SUM(C85:G85)/((((Assumptions!$C$7*(1+-0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))</f>
-        <v>1.02938493986569</v>
+        <v>1.19825172884989</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B86" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+-0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))</f>
@@ -5325,21 +5389,21 @@
         <v>409282.362942262</v>
       </c>
       <c r="G86" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.05)))+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3519794.04490555</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.05)))+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89),1,3,0))))</f>
+        <v>4365752.26416755</v>
       </c>
       <c r="H86" s="18" t="n">
         <f aca="false">IFERROR(IRR(B86:G86),"N/A")</f>
-        <v>-0.0059563132883712</v>
+        <v>0.0300313567939133</v>
       </c>
       <c r="I86" s="19" t="n">
         <f aca="false">SUM(C86:G86)/((((Assumptions!$C$7*(1+-0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))</f>
-        <v>0.975154569840683</v>
+        <v>1.13548962586823</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B87" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+-0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))</f>
@@ -5362,21 +5426,21 @@
         <v>409282.362942262</v>
       </c>
       <c r="G87" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.05)))+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3247440.14868742</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+-0.05)))+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89),1,3,0))))</f>
+        <v>4051711.90713565</v>
       </c>
       <c r="H87" s="18" t="n">
         <f aca="false">IFERROR(IRR(B87:G87),"N/A")</f>
-        <v>-0.0188552039694911</v>
+        <v>0.0173113606685587</v>
       </c>
       <c r="I87" s="19" t="n">
         <f aca="false">SUM(C87:G87)/((((Assumptions!$C$7*(1+-0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+-0.05))*Assumptions!$C$89)))</f>
-        <v>0.923535144418525</v>
+        <v>1.07596933622137</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B88" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))</f>
@@ -5399,21 +5463,21 @@
         <v>360060.846981842</v>
       </c>
       <c r="G88" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0)))+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89),1,3,0))))</f>
-        <v>4435600.27278809</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0)))+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89),1,3,0))))</f>
+        <v>5468290.11918584</v>
       </c>
       <c r="H88" s="18" t="n">
         <f aca="false">IFERROR(IRR(B88:G88),"N/A")</f>
-        <v>0.0140435461099893</v>
+        <v>0.0514789199168022</v>
       </c>
       <c r="I88" s="19" t="n">
         <f aca="false">SUM(C88:G88)/((((Assumptions!$C$7*(1+0))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))</f>
-        <v>1.06285892074421</v>
+        <v>1.24966832270182</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B89" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))</f>
@@ -5436,21 +5500,21 @@
         <v>360060.846981842</v>
       </c>
       <c r="G89" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0)))+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89),1,3,0))))</f>
-        <v>4088862.7558969</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0)))+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89),1,3,0))))</f>
+        <v>5063827.69430116</v>
       </c>
       <c r="H89" s="18" t="n">
         <f aca="false">IFERROR(IRR(B89:G89),"N/A")</f>
-        <v>3.12004312866405E-005</v>
+        <v>0.0374984454529282</v>
       </c>
       <c r="I89" s="19" t="n">
         <f aca="false">SUM(C89:G89)/((((Assumptions!$C$7*(1+0))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))</f>
-        <v>1.00013551120101</v>
+        <v>1.17650271158383</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B90" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))</f>
@@ -5473,21 +5537,21 @@
         <v>360060.846981842</v>
       </c>
       <c r="G90" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0)))+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3760537.49922862</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0)))+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89),1,3,0))))</f>
+        <v>4682487.74716997</v>
       </c>
       <c r="H90" s="18" t="n">
         <f aca="false">IFERROR(IRR(B90:G90),"N/A")</f>
-        <v>-0.0140635018559876</v>
+        <v>0.0235369032465124</v>
       </c>
       <c r="I90" s="19" t="n">
         <f aca="false">SUM(C90:G90)/((((Assumptions!$C$7*(1+0))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))</f>
-        <v>0.940742804804476</v>
+        <v>1.10751986284699</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B91" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))</f>
@@ -5510,21 +5574,21 @@
         <v>360060.846981842</v>
       </c>
       <c r="G91" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0)))+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3449195.85812542</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0)))+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89),1,3,0))))</f>
+        <v>4322342.56661607</v>
       </c>
       <c r="H91" s="18" t="n">
         <f aca="false">IFERROR(IRR(B91:G91),"N/A")</f>
-        <v>-0.0282827608031383</v>
+        <v>0.00955791635878041</v>
       </c>
       <c r="I91" s="19" t="n">
         <f aca="false">SUM(C91:G91)/((((Assumptions!$C$7*(1+0))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))</f>
-        <v>0.884422365534283</v>
+        <v>1.0423710613633</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B92" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))</f>
@@ -5547,21 +5611,21 @@
         <v>360060.846981842</v>
       </c>
       <c r="G92" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0)))+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3153553.26347797</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0)))+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0))*Assumptions!$C$89),1,3,0))))</f>
+        <v>3981672.93085808</v>
       </c>
       <c r="H92" s="18" t="n">
         <f aca="false">IFERROR(IRR(B92:G92),"N/A")</f>
-        <v>-0.0426726006677387</v>
+        <v>-0.00447642654382599</v>
       </c>
       <c r="I92" s="19" t="n">
         <f aca="false">SUM(C92:G92)/((((Assumptions!$C$7*(1+0))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0))*Assumptions!$C$89)))</f>
-        <v>0.830941820052078</v>
+        <v>0.980745306890108</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B93" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))</f>
@@ -5584,21 +5648,21 @@
         <v>310839.331021422</v>
       </c>
       <c r="G93" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.05)))+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89),1,3,0))))</f>
-        <v>4432459.69648687</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.05)))+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89),1,3,0))))</f>
+        <v>5504137.75288461</v>
       </c>
       <c r="H93" s="18" t="n">
         <f aca="false">IFERROR(IRR(B93:G93),"N/A")</f>
-        <v>-0.00363942093402338</v>
+        <v>0.0353124347506857</v>
       </c>
       <c r="I93" s="19" t="n">
         <f aca="false">SUM(C93:G93)/((((Assumptions!$C$7*(1+0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))</f>
-        <v>0.983929739567733</v>
+        <v>1.1693446966686</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B94" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))</f>
@@ -5621,21 +5685,21 @@
         <v>310839.331021422</v>
       </c>
       <c r="G94" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.05)))+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89),1,3,0))))</f>
-        <v>4055154.57360494</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.05)))+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89),1,3,0))))</f>
+        <v>5064066.07546804</v>
       </c>
       <c r="H94" s="18" t="n">
         <f aca="false">IFERROR(IRR(B94:G94),"N/A")</f>
-        <v>-0.019035295064772</v>
+        <v>0.0200731311749729</v>
       </c>
       <c r="I94" s="19" t="n">
         <f aca="false">SUM(C94:G94)/((((Assumptions!$C$7*(1+0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))</f>
-        <v>0.918650794314117</v>
+        <v>1.09320627925641</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B95" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))</f>
@@ -5658,21 +5722,21 @@
         <v>310839.331021422</v>
       </c>
       <c r="G95" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.05)))+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3698830.95952099</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.05)))+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89),1,3,0))))</f>
+        <v>4650335.2174787</v>
       </c>
       <c r="H95" s="18" t="n">
         <f aca="false">IFERROR(IRR(B95:G95),"N/A")</f>
-        <v>-0.034584761370627</v>
+        <v>0.00481041652107196</v>
       </c>
       <c r="I95" s="19" t="n">
         <f aca="false">SUM(C95:G95)/((((Assumptions!$C$7*(1+0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))</f>
-        <v>0.857001936968397</v>
+        <v>1.02162518377028</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B96" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))</f>
@@ -5695,21 +5759,21 @@
         <v>310839.331021422</v>
       </c>
       <c r="G96" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.05)))+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3361786.06262262</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.05)))+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89),1,3,0))))</f>
+        <v>4260648.92668915</v>
       </c>
       <c r="H96" s="18" t="n">
         <f aca="false">IFERROR(IRR(B96:G96),"N/A")</f>
-        <v>-0.0503470669631719</v>
+        <v>-0.0105240473336652</v>
       </c>
       <c r="I96" s="19" t="n">
         <f aca="false">SUM(C96:G96)/((((Assumptions!$C$7*(1+0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))</f>
-        <v>0.798688561298899</v>
+        <v>0.954204127177581</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B97" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))</f>
@@ -5732,21 +5796,21 @@
         <v>310839.331021422</v>
       </c>
       <c r="G97" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.05)))+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3042496.49544685</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.05)))+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89),1,3,0))))</f>
+        <v>3892970.31427103</v>
       </c>
       <c r="H97" s="18" t="n">
         <f aca="false">IFERROR(IRR(B97:G97),"N/A")</f>
-        <v>-0.0663887020694382</v>
+        <v>-0.0259818133351271</v>
       </c>
       <c r="I97" s="19" t="n">
         <f aca="false">SUM(C97:G97)/((((Assumptions!$C$7*(1+0.05))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.05))*Assumptions!$C$89)))</f>
-        <v>0.743447100444841</v>
+        <v>0.890590699860086</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B98" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))</f>
@@ -5769,21 +5833,21 @@
         <v>261617.815061002</v>
       </c>
       <c r="G98" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.1)))+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89),1,3,0))))</f>
-        <v>4414492.52067308</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.1)))+0)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89),1,3,0))))</f>
+        <v>5523954.37923084</v>
       </c>
       <c r="H98" s="18" t="n">
         <f aca="false">IFERROR(IRR(B98:G98),"N/A")</f>
-        <v>-0.0208748819342042</v>
+        <v>0.0196395922123318</v>
       </c>
       <c r="I98" s="19" t="n">
         <f aca="false">SUM(C98:G98)/((((Assumptions!$C$7*(1+0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))</f>
-        <v>0.909133698918872</v>
+        <v>1.09307098045915</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B99" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))</f>
@@ -5806,21 +5870,21 @@
         <v>261617.815061002</v>
       </c>
       <c r="G99" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.1)))+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89),1,3,0))))</f>
-        <v>4005841.04772471</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.1)))+0.0025)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89),1,3,0))))</f>
+        <v>5047372.76108527</v>
       </c>
       <c r="H99" s="18" t="n">
         <f aca="false">IFERROR(IRR(B99:G99),"N/A")</f>
-        <v>-0.0377537171102106</v>
+        <v>0.00307146201556129</v>
       </c>
       <c r="I99" s="19" t="n">
         <f aca="false">SUM(C99:G99)/((((Assumptions!$C$7*(1+0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))</f>
-        <v>0.841383518548304</v>
+        <v>1.01405868580693</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B100" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))</f>
@@ -5843,21 +5907,21 @@
         <v>261617.815061002</v>
       </c>
       <c r="G100" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.1)))+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3620933.46953383</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.1)))+0.005)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89),1,3,0))))</f>
+        <v>4600590.74322049</v>
       </c>
       <c r="H100" s="18" t="n">
         <f aca="false">IFERROR(IRR(B100:G100),"N/A")</f>
-        <v>-0.0548813739420978</v>
+        <v>-0.0135773699672616</v>
       </c>
       <c r="I100" s="19" t="n">
         <f aca="false">SUM(C100:G100)/((((Assumptions!$C$7*(1+0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))</f>
-        <v>0.777569829929285</v>
+        <v>0.939986856141731</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B101" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))</f>
@@ -5880,21 +5944,21 @@
         <v>261617.815061002</v>
       </c>
       <c r="G101" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.1)))+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89),1,3,0))))</f>
-        <v>3257758.81889505</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.1)))+0.0075)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89),1,3,0))))</f>
+        <v>4180898.10259289</v>
       </c>
       <c r="H101" s="18" t="n">
         <f aca="false">IFERROR(IRR(B101:G101),"N/A")</f>
-        <v>-0.0723413678414331</v>
+        <v>-0.0303713313778217</v>
       </c>
       <c r="I101" s="19" t="n">
         <f aca="false">SUM(C101:G101)/((((Assumptions!$C$7*(1+0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))</f>
-        <v>0.71735923553384</v>
+        <v>0.870406164562253</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B102" s="16" t="n">
         <f aca="false">-((((Assumptions!$C$7*(1+0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))</f>
@@ -5917,21 +5981,21 @@
         <v>261617.815061002</v>
       </c>
       <c r="G102" s="16" t="n">
-        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.1)))+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89),1,3,0))))</f>
-        <v>2914526.98292866</v>
+        <f aca="false">((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^4)-(-PMT(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))+(((('Operating Model'!$B$43+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))*(1+Assumptions!$C$53)^5)/((((Returns!$B$14+Assumptions!$C$20-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$16)*Assumptions!$C$14))/(Assumptions!$C$7*(1+0.1)))+0.01)+Returns!$B$36))*(1-Assumptions!$C$109)-(((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89),1,3,0))))</f>
+        <v>3785903.59940877</v>
       </c>
       <c r="H102" s="18" t="n">
         <f aca="false">IFERROR(IRR(B102:G102),"N/A")</f>
-        <v>-0.0902304161369946</v>
+        <v>-0.0473809153121889</v>
       </c>
       <c r="I102" s="19" t="n">
         <f aca="false">SUM(C102:G102)/((((Assumptions!$C$7*(1+0.1))*(1+Assumptions!$C$10)+(Capital!$B$8-Assumptions!$C$7*(1+Assumptions!$C$10)))-((Assumptions!$C$7*(1+0.1))*Assumptions!$C$89)))</f>
-        <v>0.660454953193025</v>
+        <v>0.804920168285205</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B103" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.2)))-'Unit Mix'!$D$18)))</f>
@@ -5955,20 +6019,20 @@
       </c>
       <c r="G103" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>1913234.81853303</v>
+        <v>2705773.8916669</v>
       </c>
       <c r="H103" s="18" t="n">
         <f aca="false">IFERROR(IRR(B103:G103),"N/A")</f>
-        <v>-0.129529338432886</v>
+        <v>-0.0771176338037826</v>
       </c>
       <c r="I103" s="19" t="n">
         <f aca="false">SUM(C103:G103)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.2)))-'Unit Mix'!$D$18)))</f>
-        <v>0.563914225426456</v>
+        <v>0.709874371731879</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B104" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.1)))-'Unit Mix'!$D$18)))</f>
@@ -5992,20 +6056,20 @@
       </c>
       <c r="G104" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>1913234.81853303</v>
+        <v>2705773.8916669</v>
       </c>
       <c r="H104" s="18" t="n">
         <f aca="false">IFERROR(IRR(B104:G104),"N/A")</f>
-        <v>-0.131367253706609</v>
+        <v>-0.0790303347678829</v>
       </c>
       <c r="I104" s="19" t="n">
         <f aca="false">SUM(C104:G104)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.1)))-'Unit Mix'!$D$18)))</f>
-        <v>0.558860243389553</v>
+        <v>0.703512247562237</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B105" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0)))-'Unit Mix'!$D$18)))</f>
@@ -6029,20 +6093,20 @@
       </c>
       <c r="G105" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>1913234.81853303</v>
+        <v>2705773.8916669</v>
       </c>
       <c r="H105" s="18" t="n">
         <f aca="false">IFERROR(IRR(B105:G105),"N/A")</f>
-        <v>-0.13318343348128</v>
+        <v>-0.0809206289776866</v>
       </c>
       <c r="I105" s="19" t="n">
         <f aca="false">SUM(C105:G105)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0)))-'Unit Mix'!$D$18)))</f>
-        <v>0.553896047509748</v>
+        <v>0.697263149255369</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B106" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.1)))-'Unit Mix'!$D$18)))</f>
@@ -6066,20 +6130,20 @@
       </c>
       <c r="G106" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>1913234.81853303</v>
+        <v>2705773.8916669</v>
       </c>
       <c r="H106" s="18" t="n">
         <f aca="false">IFERROR(IRR(B106:G106),"N/A")</f>
-        <v>-0.13497833608039</v>
+        <v>-0.0827889856239902</v>
       </c>
       <c r="I106" s="19" t="n">
         <f aca="false">SUM(C106:G106)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.1)))-'Unit Mix'!$D$18)))</f>
-        <v>0.549019266218657</v>
+        <v>0.691124091400482</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B107" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.2)))-'Unit Mix'!$D$18)))</f>
@@ -6103,20 +6167,20 @@
       </c>
       <c r="G107" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((100-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>1913234.81853303</v>
+        <v>2705773.8916669</v>
       </c>
       <c r="H107" s="18" t="n">
         <f aca="false">IFERROR(IRR(B107:G107),"N/A")</f>
-        <v>-0.136752406039614</v>
+        <v>-0.0846358598627693</v>
       </c>
       <c r="I107" s="19" t="n">
         <f aca="false">SUM(C107:G107)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.2)))-'Unit Mix'!$D$18)))</f>
-        <v>0.544227610740903</v>
+        <v>0.685092192809427</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B108" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.2)))-'Unit Mix'!$D$18)))</f>
@@ -6140,20 +6204,20 @@
       </c>
       <c r="G108" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2103100.73002555</v>
+        <v>2908940.69365176</v>
       </c>
       <c r="H108" s="18" t="n">
         <f aca="false">IFERROR(IRR(B108:G108),"N/A")</f>
-        <v>-0.112790008081192</v>
+        <v>-0.062955717752434</v>
       </c>
       <c r="I108" s="19" t="n">
         <f aca="false">SUM(C108:G108)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.2)))-'Unit Mix'!$D$18)))</f>
-        <v>0.608826464238361</v>
+        <v>0.757236205760052</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B109" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.1)))-'Unit Mix'!$D$18)))</f>
@@ -6177,20 +6241,20 @@
       </c>
       <c r="G109" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2103100.73002555</v>
+        <v>2908940.69365176</v>
       </c>
       <c r="H109" s="18" t="n">
         <f aca="false">IFERROR(IRR(B109:G109),"N/A")</f>
-        <v>-0.114664077662226</v>
+        <v>-0.0649006747100014</v>
       </c>
       <c r="I109" s="19" t="n">
         <f aca="false">SUM(C109:G109)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.1)))-'Unit Mix'!$D$18)))</f>
-        <v>0.603369964162441</v>
+        <v>0.75044960948522</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B110" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0)))-'Unit Mix'!$D$18)))</f>
@@ -6214,20 +6278,20 @@
       </c>
       <c r="G110" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2103100.73002555</v>
+        <v>2908940.69365176</v>
       </c>
       <c r="H110" s="18" t="n">
         <f aca="false">IFERROR(IRR(B110:G110),"N/A")</f>
-        <v>-0.116515979431841</v>
+        <v>-0.0668228295496783</v>
       </c>
       <c r="I110" s="19" t="n">
         <f aca="false">SUM(C110:G110)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0)))-'Unit Mix'!$D$18)))</f>
-        <v>0.598010401149106</v>
+        <v>0.743783580002047</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B111" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.1)))-'Unit Mix'!$D$18)))</f>
@@ -6251,20 +6315,20 @@
       </c>
       <c r="G111" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2103100.73002555</v>
+        <v>2908940.69365176</v>
       </c>
       <c r="H111" s="18" t="n">
         <f aca="false">IFERROR(IRR(B111:G111),"N/A")</f>
-        <v>-0.118346180892634</v>
+        <v>-0.068722660004182</v>
       </c>
       <c r="I111" s="19" t="n">
         <f aca="false">SUM(C111:G111)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.1)))-'Unit Mix'!$D$18)))</f>
-        <v>0.592745214749396</v>
+        <v>0.737234932717268</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B112" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.2)))-'Unit Mix'!$D$18)))</f>
@@ -6288,20 +6352,20 @@
       </c>
       <c r="G112" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((137.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2103100.73002555</v>
+        <v>2908940.69365176</v>
       </c>
       <c r="H112" s="18" t="n">
         <f aca="false">IFERROR(IRR(B112:G112),"N/A")</f>
-        <v>-0.12015513548199</v>
+        <v>-0.0706006295096657</v>
       </c>
       <c r="I112" s="19" t="n">
         <f aca="false">SUM(C112:G112)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.2)))-'Unit Mix'!$D$18)))</f>
-        <v>0.587571933901297</v>
+        <v>0.730800594213855</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B113" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.2)))-'Unit Mix'!$D$18)))</f>
@@ -6325,20 +6389,20 @@
       </c>
       <c r="G113" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2292966.64151808</v>
+        <v>3112107.49563662</v>
       </c>
       <c r="H113" s="18" t="n">
         <f aca="false">IFERROR(IRR(B113:G113),"N/A")</f>
-        <v>-0.0971144954430443</v>
+        <v>-0.0495048935188046</v>
       </c>
       <c r="I113" s="19" t="n">
         <f aca="false">SUM(C113:G113)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.2)))-'Unit Mix'!$D$18)))</f>
-        <v>0.653738703050266</v>
+        <v>0.804598039788225</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B114" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.1)))-'Unit Mix'!$D$18)))</f>
@@ -6362,20 +6426,20 @@
       </c>
       <c r="G114" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2292966.64151808</v>
+        <v>3112107.49563662</v>
       </c>
       <c r="H114" s="18" t="n">
         <f aca="false">IFERROR(IRR(B114:G114),"N/A")</f>
-        <v>-0.0990228799637324</v>
+        <v>-0.0514807762452103</v>
       </c>
       <c r="I114" s="19" t="n">
         <f aca="false">SUM(C114:G114)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.1)))-'Unit Mix'!$D$18)))</f>
-        <v>0.647879684935329</v>
+        <v>0.797386971408204</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B115" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0)))-'Unit Mix'!$D$18)))</f>
@@ -6399,20 +6463,20 @@
       </c>
       <c r="G115" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2292966.64151808</v>
+        <v>3112107.49563662</v>
       </c>
       <c r="H115" s="18" t="n">
         <f aca="false">IFERROR(IRR(B115:G115),"N/A")</f>
-        <v>-0.100908683338398</v>
+        <v>-0.053433475853638</v>
       </c>
       <c r="I115" s="19" t="n">
         <f aca="false">SUM(C115:G115)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0)))-'Unit Mix'!$D$18)))</f>
-        <v>0.642124754788466</v>
+        <v>0.790304010748724</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B116" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.1)))-'Unit Mix'!$D$18)))</f>
@@ -6436,20 +6500,20 @@
       </c>
       <c r="G116" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2292966.64151808</v>
+        <v>3112107.49563662</v>
       </c>
       <c r="H116" s="18" t="n">
         <f aca="false">IFERROR(IRR(B116:G116),"N/A")</f>
-        <v>-0.102772381894187</v>
+        <v>-0.055363478339491</v>
       </c>
       <c r="I116" s="19" t="n">
         <f aca="false">SUM(C116:G116)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.1)))-'Unit Mix'!$D$18)))</f>
-        <v>0.636471163280136</v>
+        <v>0.783345774034054</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B117" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.2)))-'Unit Mix'!$D$18)))</f>
@@ -6473,20 +6537,20 @@
       </c>
       <c r="G117" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((175-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2292966.64151808</v>
+        <v>3112107.49563662</v>
       </c>
       <c r="H117" s="18" t="n">
         <f aca="false">IFERROR(IRR(B117:G117),"N/A")</f>
-        <v>-0.104614437625108</v>
+        <v>-0.05727125514765</v>
       </c>
       <c r="I117" s="19" t="n">
         <f aca="false">SUM(C117:G117)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.2)))-'Unit Mix'!$D$18)))</f>
-        <v>0.630916257061692</v>
+        <v>0.776508995618284</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B118" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.2)))-'Unit Mix'!$D$18)))</f>
@@ -6510,20 +6574,20 @@
       </c>
       <c r="G118" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2482832.5530106</v>
+        <v>3315274.29762149</v>
       </c>
       <c r="H118" s="18" t="n">
         <f aca="false">IFERROR(IRR(B118:G118),"N/A")</f>
-        <v>-0.0823536615596951</v>
+        <v>-0.0366847941525038</v>
       </c>
       <c r="I118" s="19" t="n">
         <f aca="false">SUM(C118:G118)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.2)))-'Unit Mix'!$D$18)))</f>
-        <v>0.69865094186217</v>
+        <v>0.851959873816398</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B119" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.1)))-'Unit Mix'!$D$18)))</f>
@@ -6547,20 +6611,20 @@
       </c>
       <c r="G119" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2482832.5530106</v>
+        <v>3315274.29762149</v>
       </c>
       <c r="H119" s="18" t="n">
         <f aca="false">IFERROR(IRR(B119:G119),"N/A")</f>
-        <v>-0.0842947647910973</v>
+        <v>-0.0386904189301734</v>
       </c>
       <c r="I119" s="19" t="n">
         <f aca="false">SUM(C119:G119)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.1)))-'Unit Mix'!$D$18)))</f>
-        <v>0.692389405708216</v>
+        <v>0.844324333331187</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B120" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0)))-'Unit Mix'!$D$18)))</f>
@@ -6584,20 +6648,20 @@
       </c>
       <c r="G120" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2482832.5530106</v>
+        <v>3315274.29762149</v>
       </c>
       <c r="H120" s="18" t="n">
         <f aca="false">IFERROR(IRR(B120:G120),"N/A")</f>
-        <v>-0.0862128901036781</v>
+        <v>-0.0406724923911844</v>
       </c>
       <c r="I120" s="19" t="n">
         <f aca="false">SUM(C120:G120)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0)))-'Unit Mix'!$D$18)))</f>
-        <v>0.686239108427824</v>
+        <v>0.836824441495402</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B121" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.1)))-'Unit Mix'!$D$18)))</f>
@@ -6621,20 +6685,20 @@
       </c>
       <c r="G121" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2482832.5530106</v>
+        <v>3315274.29762149</v>
       </c>
       <c r="H121" s="18" t="n">
         <f aca="false">IFERROR(IRR(B121:G121),"N/A")</f>
-        <v>-0.0881085223381404</v>
+        <v>-0.0426315085444882</v>
       </c>
       <c r="I121" s="19" t="n">
         <f aca="false">SUM(C121:G121)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.1)))-'Unit Mix'!$D$18)))</f>
-        <v>0.680197111810875</v>
+        <v>0.829456615350839</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B122" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.2)))-'Unit Mix'!$D$18)))</f>
@@ -6658,20 +6722,20 @@
       </c>
       <c r="G122" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((212.5-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2482832.5530106</v>
+        <v>3315274.29762149</v>
       </c>
       <c r="H122" s="18" t="n">
         <f aca="false">IFERROR(IRR(B122:G122),"N/A")</f>
-        <v>-0.0899821317424673</v>
+        <v>-0.0445679466015034</v>
       </c>
       <c r="I122" s="19" t="n">
         <f aca="false">SUM(C122:G122)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.2)))-'Unit Mix'!$D$18)))</f>
-        <v>0.674260580222086</v>
+        <v>0.822217397022712</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B123" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.2)))-'Unit Mix'!$D$18)))</f>
@@ -6695,20 +6759,20 @@
       </c>
       <c r="G123" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2672698.46450312</v>
+        <v>3518441.09960635</v>
       </c>
       <c r="H123" s="18" t="n">
         <f aca="false">IFERROR(IRR(B123:G123),"N/A")</f>
-        <v>-0.0683887101893623</v>
+        <v>-0.0244284060339821</v>
       </c>
       <c r="I123" s="19" t="n">
         <f aca="false">SUM(C123:G123)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.2)))-'Unit Mix'!$D$18)))</f>
-        <v>0.743563180674075</v>
+        <v>0.899321707844571</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B124" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.1)))-'Unit Mix'!$D$18)))</f>
@@ -6732,20 +6796,20 @@
       </c>
       <c r="G124" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2672698.46450312</v>
+        <v>3518441.09960635</v>
       </c>
       <c r="H124" s="18" t="n">
         <f aca="false">IFERROR(IRR(B124:G124),"N/A")</f>
-        <v>-0.0703611319179342</v>
+        <v>-0.026462711775903</v>
       </c>
       <c r="I124" s="19" t="n">
         <f aca="false">SUM(C124:G124)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+-0.1)))-'Unit Mix'!$D$18)))</f>
-        <v>0.736899126481104</v>
+        <v>0.891261695254171</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B125" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0)))-'Unit Mix'!$D$18)))</f>
@@ -6769,20 +6833,20 @@
       </c>
       <c r="G125" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2672698.46450312</v>
+        <v>3518441.09960635</v>
       </c>
       <c r="H125" s="18" t="n">
         <f aca="false">IFERROR(IRR(B125:G125),"N/A")</f>
-        <v>-0.0723101935522196</v>
+        <v>-0.0284731094931717</v>
       </c>
       <c r="I125" s="19" t="n">
         <f aca="false">SUM(C125:G125)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0)))-'Unit Mix'!$D$18)))</f>
-        <v>0.730353462067183</v>
+        <v>0.883344872242079</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B126" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.1)))-'Unit Mix'!$D$18)))</f>
@@ -6806,20 +6870,20 @@
       </c>
       <c r="G126" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2672698.46450312</v>
+        <v>3518441.09960635</v>
       </c>
       <c r="H126" s="18" t="n">
         <f aca="false">IFERROR(IRR(B126:G126),"N/A")</f>
-        <v>-0.0742363881712281</v>
+        <v>-0.0304601009844406</v>
       </c>
       <c r="I126" s="19" t="n">
         <f aca="false">SUM(C126:G126)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.1)))-'Unit Mix'!$D$18)))</f>
-        <v>0.723923060341614</v>
+        <v>0.875567456667625</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B127" s="16" t="n">
         <f aca="false">-((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.2)))-'Unit Mix'!$D$18)))</f>
@@ -6843,15 +6907,15 @@
       </c>
       <c r="G127" s="16" t="n">
         <f aca="false">((('Operating Model'!$B$43+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10))-(-PMT(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9))+((((('Operating Model'!$B$43+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10)*Assumptions!$C$38)+((250-Assumptions!$C$36)*12*'Unit Mix'!$C$10))*(1+Assumptions!$C$53))/(Returns!$B$34+Returns!$B$36))*(1-Assumptions!$C$109)-(Debt!$C$9+CUMPRINC(Assumptions!$C$88,Assumptions!$C$93,Debt!$C$9,1,3,0))))</f>
-        <v>2672698.46450312</v>
+        <v>3518441.09960635</v>
       </c>
       <c r="H127" s="18" t="n">
         <f aca="false">IFERROR(IRR(B127:G127),"N/A")</f>
-        <v>-0.0761401940091858</v>
+        <v>-0.0324241730100852</v>
       </c>
       <c r="I127" s="19" t="n">
         <f aca="false">SUM(C127:G127)/((Capital!$B$12+(('Unit Mix'!$C$10*(Assumptions!$C$34*(1+0.2)))-'Unit Mix'!$D$18)))</f>
-        <v>0.71760490338248</v>
+        <v>0.867925798427141</v>
       </c>
     </row>
   </sheetData>
@@ -6870,7 +6934,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -6880,19 +6944,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B5" s="20" t="n">
         <f aca="false">Capital!$B$19</f>
@@ -6905,14 +6969,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B8" s="20" t="n">
         <f aca="false">('Operating Model'!B$49-Debt!$E$18)-Returns!C50</f>
@@ -6925,7 +6989,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">('Operating Model'!C$49-Debt!$E$19)-Returns!D50</f>
@@ -6938,7 +7002,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B10" s="20" t="n">
         <f aca="false">('Operating Model'!D$49-Debt!$E$20)-Returns!E50</f>
@@ -6951,7 +7015,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B11" s="20" t="n">
         <f aca="false">('Operating Model'!E$49-Debt!$E$21)-Returns!F50</f>
@@ -6964,7 +7028,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B12" s="20" t="n">
         <f aca="false">('Operating Model'!F$49-Debt!$E$22)-Returns!G50</f>
@@ -6977,14 +7041,14 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B15" s="20" t="n">
         <f aca="false">'Operating Model'!B28+'Operating Model'!B41-'Operating Model'!B43</f>
@@ -6997,7 +7061,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B16" s="20" t="n">
         <f aca="false">'Operating Model'!C28+'Operating Model'!C41-'Operating Model'!C43</f>
@@ -7010,7 +7074,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B17" s="20" t="n">
         <f aca="false">'Operating Model'!D28+'Operating Model'!D41-'Operating Model'!D43</f>
@@ -7023,7 +7087,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B18" s="20" t="n">
         <f aca="false">'Operating Model'!E28+'Operating Model'!E41-'Operating Model'!E43</f>
@@ -7036,7 +7100,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B19" s="20" t="n">
         <f aca="false">'Operating Model'!F28+'Operating Model'!F41-'Operating Model'!F43</f>
@@ -7049,14 +7113,14 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B22" s="20" t="n">
         <f aca="false">Waterfall!C34</f>
@@ -7069,7 +7133,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B23" s="20" t="n">
         <f aca="false">Waterfall!D34</f>
@@ -7082,7 +7146,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B24" s="20" t="n">
         <f aca="false">Waterfall!E34</f>
@@ -7095,7 +7159,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B25" s="20" t="n">
         <f aca="false">Waterfall!F34</f>
@@ -7108,7 +7172,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B26" s="20" t="n">
         <f aca="false">Waterfall!G34</f>
@@ -7121,18 +7185,18 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B29" s="20" t="n">
         <f aca="false">MIN(Waterfall!C11:G11)</f>
-        <v>1187043.27264836</v>
+        <v>0</v>
       </c>
       <c r="C29" s="0" t="str">
         <f aca="false">IF(B29&gt;=-0.01,"OK","FAIL")</f>
@@ -7141,11 +7205,11 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B30" s="20" t="n">
         <f aca="false">MIN(Waterfall!C17:G17)</f>
-        <v>2526367.86454093</v>
+        <v>609344.720521759</v>
       </c>
       <c r="C30" s="0" t="str">
         <f aca="false">IF(B30&gt;=-0.01,"OK","FAIL")</f>
@@ -7154,14 +7218,14 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B33" s="20" t="n">
         <f aca="false">Capital!$B$16+Capital!$B$17-Capital!$B$12</f>
@@ -7172,76 +7236,89 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="B34" s="20" t="n">
+        <f aca="false">'Returns (Assumed)'!$B$10+'Returns (Assumed)'!$B$11-'Returns (Assumed)'!$B$9</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="0" t="str">
+        <f aca="false">IF(ABS(B34)&lt;0.01,"OK","FAIL")</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>488</v>
-      </c>
-      <c r="B36" s="20" t="n">
+      <c r="A36" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="B37" s="20" t="n">
         <f aca="false">Debt!$C$9-SUM(Debt!D18:D22)-Debt!F22</f>
         <v>0</v>
       </c>
-      <c r="C36" s="0" t="str">
-        <f aca="false">IF(ABS(B36)&lt;0.01,"OK","FAIL")</f>
+      <c r="C37" s="0" t="str">
+        <f aca="false">IF(ABS(B37)&lt;0.01,"OK","FAIL")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-    </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>490</v>
-      </c>
-      <c r="B39" s="20" t="n">
+      <c r="A39" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="B40" s="20" t="n">
         <f aca="false">Returns!B25-'Operating Model'!$B$43</f>
         <v>0</v>
       </c>
-      <c r="C39" s="0" t="str">
-        <f aca="false">IF(ABS(B39)&lt;0.01,"OK","FAIL")</f>
+      <c r="C40" s="0" t="str">
+        <f aca="false">IF(ABS(B40)&lt;0.01,"OK","FAIL")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-    </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>492</v>
-      </c>
-      <c r="B42" s="20" t="n">
+      <c r="A42" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="B43" s="20" t="n">
         <f aca="false">'Debt (Assumed)'!$B$24-SUM('Debt (Assumed)'!C31:F31)-'Debt (Assumed)'!F32</f>
         <v>0</v>
       </c>
-      <c r="C42" s="0" t="str">
-        <f aca="false">IF(ABS(B42)&lt;0.01,"OK","FAIL")</f>
+      <c r="C43" s="0" t="str">
+        <f aca="false">IF(ABS(B43)&lt;0.01,"OK","FAIL")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-    </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
-        <v>494</v>
+      <c r="A45" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -7260,7 +7337,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -7270,17 +7347,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B6" s="3"/>
     </row>
@@ -7295,52 +7372,52 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">Capital!$B$8</f>
-        <v>14498040</v>
+        <f aca="false">'Returns (Assumed)'!$B$7</f>
+        <v>14545290</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">Debt!$C$9</f>
-        <v>8970000</v>
+        <f aca="false">'Returns (Assumed)'!$B$8</f>
+        <v>9450000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="B10" s="16" t="n">
-        <f aca="false">Capital!$B$12</f>
-        <v>5528040</v>
+      <c r="B10" s="10" t="n">
+        <f aca="false">'Returns (Assumed)'!$B$9</f>
+        <v>5095290</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>500</v>
+        <v>317</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">Capital!$B$16</f>
-        <v>4975236</v>
+        <f aca="false">'Returns (Assumed)'!$B$10</f>
+        <v>4585761</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">Capital!$B$17</f>
-        <v>552804</v>
+        <f aca="false">'Returns (Assumed)'!$B$11</f>
+        <v>509529</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B14" s="3"/>
     </row>
@@ -7355,7 +7432,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">Returns!$B$29</f>
@@ -7364,229 +7441,307 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B17" s="18" t="n">
-        <f aca="false">Returns!$B$33</f>
+        <f aca="false">Returns!B30</f>
         <v>0.0722959213632609</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B18" s="18" t="n">
         <f aca="false">Returns!$B$34</f>
-        <v>0.0772959213632609</v>
+        <v>0.0705973844782609</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B19" s="18" t="n">
-        <f aca="false">Debt!C9/Assumptions!$C$7</f>
-        <v>0.65</v>
+        <f aca="false">'Returns (Assumed)'!$B$8/Assumptions!$C$7</f>
+        <v>0.684782608695652</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="B20" s="0" t="str">
-        <f aca="false">Debt!C10</f>
-        <v>LTV</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>508</v>
-      </c>
-      <c r="B21" s="22" t="n">
+        <v>509</v>
+      </c>
+      <c r="B20" s="22" t="n">
         <f aca="false">Assumptions!$C$106</f>
         <v>5</v>
       </c>
     </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B22" s="3"/>
+    </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="B23" s="3"/>
+      <c r="A23" s="0" t="s">
+        <v>511</v>
+      </c>
+      <c r="B23" s="18" t="n">
+        <f aca="false">Returns!B57</f>
+        <v>0.0631645276549801</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>281</v>
-      </c>
-      <c r="B24" s="18" t="n">
-        <f aca="false">Returns!B57</f>
-        <v>0.0502576440792279</v>
+      <c r="A24" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="B24" s="11" t="n">
+        <f aca="false">'Returns (Assumed)'!B30</f>
+        <v>0.0807266925391043</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="B25" s="18" t="n">
-        <f aca="false">Returns!B58</f>
-        <v>0.0148422254374714</v>
+        <v>513</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <f aca="false">Returns!B59</f>
+        <v>1.31637334554738</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>283</v>
-      </c>
-      <c r="B26" s="19" t="n">
-        <f aca="false">Returns!B59</f>
-        <v>1.24490401829805</v>
+      <c r="A26" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="B26" s="23" t="n">
+        <f aca="false">'Returns (Assumed)'!B31</f>
+        <v>1.40689645116955</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>511</v>
-      </c>
-      <c r="B27" s="19" t="n">
-        <f aca="false">Returns!B60</f>
-        <v>1.06993687925323</v>
+        <v>353</v>
+      </c>
+      <c r="B27" s="18" t="n">
+        <f aca="false">Waterfall!B37</f>
+        <v>0.0995543216063557</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>351</v>
-      </c>
-      <c r="B28" s="18" t="n">
-        <f aca="false">Waterfall!B37</f>
-        <v>0.038533660287425</v>
+        <v>355</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <f aca="false">Waterfall!B39</f>
+        <v>1.51281228739731</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>353</v>
-      </c>
-      <c r="B29" s="19" t="n">
-        <f aca="false">Waterfall!B39</f>
-        <v>1.18881875472581</v>
+        <v>354</v>
+      </c>
+      <c r="B29" s="18" t="n">
+        <f aca="false">Waterfall!B38</f>
+        <v>-0.14622204957911</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>352</v>
-      </c>
-      <c r="B30" s="18" t="str">
-        <f aca="false">Waterfall!B38</f>
-        <v>N/A - GP receives $0 in this scenario, IRR undefined</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>354</v>
-      </c>
-      <c r="B31" s="19" t="n">
+        <v>356</v>
+      </c>
+      <c r="B30" s="19" t="n">
         <f aca="false">Waterfall!B40</f>
-        <v>0</v>
-      </c>
+        <v>0.45365392511974</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
+      <c r="B33" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="14" t="s">
-        <v>513</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>514</v>
+      <c r="A34" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="B34" s="16" t="n">
+        <f aca="false">'Returns (Assumed)'!$B$8</f>
+        <v>9450000</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <f aca="false">Debt!$C$9</f>
+        <v>8970000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>515</v>
-      </c>
-      <c r="B35" s="16" t="n">
-        <f aca="false">Debt!$C$9</f>
-        <v>8970000</v>
-      </c>
-      <c r="C35" s="16" t="n">
-        <f aca="false">'Returns (Assumed)'!$B$8</f>
-        <v>9450000</v>
+        <v>519</v>
+      </c>
+      <c r="B35" s="18" t="n">
+        <f aca="false">Assumptions!$C$101</f>
+        <v>0.0420651851851852</v>
+      </c>
+      <c r="C35" s="18" t="n">
+        <f aca="false">Assumptions!$C$88</f>
+        <v>0.071</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>516</v>
-      </c>
-      <c r="B36" s="18" t="n">
-        <f aca="false">Assumptions!$C$88</f>
-        <v>0.071</v>
-      </c>
-      <c r="C36" s="18" t="n">
-        <f aca="false">Assumptions!$C$101</f>
-        <v>0.0420651851851852</v>
+        <v>520</v>
+      </c>
+      <c r="B36" s="16" t="n">
+        <f aca="false">'Returns (Assumed)'!$B$9</f>
+        <v>5095290</v>
+      </c>
+      <c r="C36" s="16" t="n">
+        <f aca="false">Capital!$B$12</f>
+        <v>5528040</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>517</v>
-      </c>
-      <c r="B37" s="16" t="n">
-        <f aca="false">Capital!$B$12</f>
-        <v>5528040</v>
-      </c>
-      <c r="C37" s="16" t="n">
-        <f aca="false">'Returns (Assumed)'!$B$9</f>
-        <v>5095290</v>
+        <v>512</v>
+      </c>
+      <c r="B37" s="18" t="n">
+        <f aca="false">'Returns (Assumed)'!B30</f>
+        <v>0.0807266925391043</v>
+      </c>
+      <c r="C37" s="18" t="n">
+        <f aca="false">Returns!B58</f>
+        <v>0.050695834311719</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="B38" s="18" t="n">
-        <f aca="false">Returns!B58</f>
-        <v>0.0148422254374714</v>
-      </c>
-      <c r="C38" s="18" t="n">
-        <f aca="false">'Returns (Assumed)'!B28</f>
-        <v>0.0436954779740151</v>
+        <v>514</v>
+      </c>
+      <c r="B38" s="19" t="n">
+        <f aca="false">'Returns (Assumed)'!B31</f>
+        <v>1.40689645116955</v>
+      </c>
+      <c r="C38" s="19" t="n">
+        <f aca="false">Returns!B60</f>
+        <v>1.25737495228343</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>511</v>
-      </c>
-      <c r="B39" s="19" t="n">
-        <f aca="false">Returns!B60</f>
-        <v>1.06993687925323</v>
-      </c>
-      <c r="C39" s="19" t="n">
-        <f aca="false">'Returns (Assumed)'!B29</f>
-        <v>1.20353900434437</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>326</v>
-      </c>
-      <c r="B40" s="18" t="n">
+        <v>328</v>
+      </c>
+      <c r="B39" s="18" t="n">
+        <f aca="false">'Returns (Assumed)'!B32</f>
+        <v>0.112077568659095</v>
+      </c>
+      <c r="C39" s="18" t="n">
         <f aca="false">Returns!C50/Returns!B55</f>
         <v>0.060005664722578</v>
       </c>
-      <c r="C40" s="18" t="n">
-        <f aca="false">'Returns (Assumed)'!B30</f>
-        <v>0.112077568659095</v>
-      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="B42" s="3"/>
-    </row>
-    <row r="43" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="21" t="s">
-        <v>519</v>
+      <c r="A42" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>525</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>526</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="B44" s="16" t="n">
+        <v>15471922</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>529</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>0.056687</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="s">
+        <v>531</v>
+      </c>
+      <c r="B45" s="16" t="n">
+        <v>12294971</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>532</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>0.075691</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="s">
+        <v>534</v>
+      </c>
+      <c r="B46" s="16" t="n">
+        <v>11552192</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>535</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>0.081642</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="B49" s="3"/>
+    </row>
+    <row r="50" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21" t="s">
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -10273,9 +10428,9 @@
       <c r="A33" s="0" t="s">
         <v>254</v>
       </c>
-      <c r="B33" s="18" t="n">
-        <f aca="false">'Operating Model'!$B$43/Assumptions!$C$7</f>
-        <v>0.0722959213632609</v>
+      <c r="B33" s="11" t="n">
+        <f aca="false">Returns!$B$29</f>
+        <v>0.0655973844782609</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10284,7 +10439,7 @@
       </c>
       <c r="B34" s="18" t="n">
         <f aca="false">Returns!$B$33+Assumptions!$C$107</f>
-        <v>0.0772959213632609</v>
+        <v>0.0705973844782609</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10293,7 +10448,7 @@
       </c>
       <c r="B35" s="18" t="n">
         <f aca="false">Returns!$B$33+Assumptions!$C$108</f>
-        <v>0.0822959213632609</v>
+        <v>0.0755973844782609</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10320,7 +10475,7 @@
       </c>
       <c r="B38" s="10" t="n">
         <f aca="false">Returns!$B$37/(Returns!$B$34+Returns!$B$36)</f>
-        <v>13805011.5455902</v>
+        <v>14862322.938686</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10329,7 +10484,7 @@
       </c>
       <c r="B39" s="16" t="n">
         <f aca="false">-Returns!$B$38*Assumptions!$C$109</f>
-        <v>-276100.230911803</v>
+        <v>-297246.458773719</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10347,7 +10502,7 @@
       </c>
       <c r="B41" s="10" t="n">
         <f aca="false">Returns!$B$38+Returns!$B$39+Returns!$B$40</f>
-        <v>4859042.18418345</v>
+        <v>5895207.34941733</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10356,7 +10511,7 @@
       </c>
       <c r="B42" s="16" t="n">
         <f aca="false">Returns!$B$38+Returns!$B$39</f>
-        <v>13528911.3146784</v>
+        <v>14565076.4799122</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10434,7 +10589,7 @@
       </c>
       <c r="G47" s="16" t="n">
         <f aca="false">Returns!$B$42</f>
-        <v>13528911.3146784</v>
+        <v>14565076.4799122</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10463,7 +10618,7 @@
       </c>
       <c r="G48" s="10" t="n">
         <f aca="false">G46+G47</f>
-        <v>14435298.6551564</v>
+        <v>15471463.8203903</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10534,7 +10689,7 @@
       </c>
       <c r="G51" s="16" t="n">
         <f aca="false">Returns!$B$41</f>
-        <v>4859042.18418345</v>
+        <v>5895207.34941733</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10563,7 +10718,7 @@
       </c>
       <c r="G52" s="10" t="n">
         <f aca="false">G50+G51</f>
-        <v>5035294.43900686</v>
+        <v>6071459.60424074</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10596,7 +10751,7 @@
       </c>
       <c r="B57" s="18" t="n">
         <f aca="false">IFERROR(IRR(B48:G48),"N/A - no sign change / undefined")</f>
-        <v>0.0502576440792279</v>
+        <v>0.0631645276549801</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10605,7 +10760,7 @@
       </c>
       <c r="B58" s="18" t="n">
         <f aca="false">IFERROR(IRR(B52:G52),"N/A - no sign change / undefined")</f>
-        <v>0.0148422254374714</v>
+        <v>0.050695834311719</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10614,7 +10769,7 @@
       </c>
       <c r="B59" s="19" t="n">
         <f aca="false">SUM(C48:G48)/B56</f>
-        <v>1.24490401829805</v>
+        <v>1.31637334554738</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10623,7 +10778,7 @@
       </c>
       <c r="B60" s="19" t="n">
         <f aca="false">SUM(C52:G52)/B55</f>
-        <v>1.06993687925323</v>
+        <v>1.25737495228343</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11256,7 +11411,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
@@ -11320,131 +11475,99 @@
         <v>317</v>
       </c>
       <c r="B10" s="16" t="n">
+        <f aca="false">'Returns (Assumed)'!$B$9*(1-Assumptions!$C$118)</f>
+        <v>4585761</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <f aca="false">'Returns (Assumed)'!$B$9*Assumptions!$C$118</f>
+        <v>509529</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>319</v>
+      </c>
+      <c r="B12" s="16" t="n">
         <f aca="false">Capital!$B$12</f>
         <v>5528040</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>319</v>
-      </c>
-      <c r="B13" s="16" t="n">
-        <f aca="false">Returns!$B$38</f>
-        <v>13805011.5455902</v>
-      </c>
-    </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>260</v>
-      </c>
-      <c r="B14" s="16" t="n">
-        <f aca="false">-B13*Assumptions!$C$109</f>
-        <v>-276100.230911803</v>
-      </c>
+      <c r="A14" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B15" s="16" t="n">
+        <f aca="false">Returns!$B$38</f>
+        <v>14862322.938686</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="B16" s="16" t="n">
+        <f aca="false">-B15*Assumptions!$C$109</f>
+        <v>-297246.458773719</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="B17" s="16" t="n">
         <f aca="false">-'Debt (Assumed)'!F$38</f>
         <v>-8970000</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="B16" s="10" t="n">
-        <f aca="false">B13+B14+B15</f>
-        <v>4558911.31467836</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="B18" s="10" t="n">
+        <f aca="false">B15+B16+B17</f>
+        <v>5595076.47991224</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="14" t="s">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C21" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D21" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E21" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F21" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G21" s="14" t="s">
         <v>270</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>321</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <f aca="false">'Operating Model'!$B$49</f>
-        <v>968583.714813</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <f aca="false">'Operating Model'!$C$49</f>
-        <v>790159.86326819</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <f aca="false">'Operating Model'!$D$49</f>
-        <v>934046.9828656</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <f aca="false">'Operating Model'!$E$49</f>
-        <v>920579.037342633</v>
-      </c>
-      <c r="G20" s="16" t="n">
-        <f aca="false">'Operating Model'!$F$49</f>
-        <v>906387.340478033</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>322</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <f aca="false">-'Debt (Assumed)'!B$37</f>
-        <v>-397516</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <f aca="false">-'Debt (Assumed)'!C$37</f>
-        <v>-397516</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <f aca="false">-'Debt (Assumed)'!D$37</f>
-        <v>-397516</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <f aca="false">-'Debt (Assumed)'!E$37</f>
-        <v>-636870</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <f aca="false">-'Debt (Assumed)'!F$37</f>
-        <v>-636870</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11452,131 +11575,181 @@
         <v>323</v>
       </c>
       <c r="C22" s="16" t="n">
+        <f aca="false">'Operating Model'!$B$49</f>
+        <v>968583.714813</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <f aca="false">'Operating Model'!$C$49</f>
+        <v>790159.86326819</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <f aca="false">'Operating Model'!$D$49</f>
+        <v>934046.9828656</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <f aca="false">'Operating Model'!$E$49</f>
+        <v>920579.037342633</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <f aca="false">'Operating Model'!$F$49</f>
+        <v>906387.340478033</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="C23" s="16" t="n">
+        <f aca="false">-'Debt (Assumed)'!B$37</f>
+        <v>-397516</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <f aca="false">-'Debt (Assumed)'!C$37</f>
+        <v>-397516</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <f aca="false">-'Debt (Assumed)'!D$37</f>
+        <v>-397516</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <f aca="false">-'Debt (Assumed)'!E$37</f>
+        <v>-636870</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <f aca="false">-'Debt (Assumed)'!F$37</f>
+        <v>-636870</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="C24" s="16" t="n">
         <f aca="false">-IF(1=Assumptions!$C$98,'Debt (Assumed)'!$B$25,0)</f>
         <v>-0</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D24" s="16" t="n">
         <f aca="false">-IF(2=Assumptions!$C$98,'Debt (Assumed)'!$B$25,0)</f>
         <v>-0</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E24" s="16" t="n">
         <f aca="false">-IF(3=Assumptions!$C$98,'Debt (Assumed)'!$B$25,0)</f>
         <v>-480000</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F24" s="16" t="n">
         <f aca="false">-IF(4=Assumptions!$C$98,'Debt (Assumed)'!$B$25,0)</f>
         <v>-0</v>
       </c>
-      <c r="G22" s="16" t="n">
+      <c r="G24" s="16" t="n">
         <f aca="false">-IF(5=Assumptions!$C$98,'Debt (Assumed)'!$B$25,0)</f>
         <v>-0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>275</v>
       </c>
-      <c r="C23" s="16" t="n">
-        <f aca="false">C20+C21+C22</f>
+      <c r="C25" s="16" t="n">
+        <f aca="false">C22+C23+C24</f>
         <v>571067.714813</v>
       </c>
-      <c r="D23" s="16" t="n">
-        <f aca="false">D20+D21+D22</f>
+      <c r="D25" s="16" t="n">
+        <f aca="false">D22+D23+D24</f>
         <v>392643.86326819</v>
       </c>
-      <c r="E23" s="16" t="n">
-        <f aca="false">E20+E21+E22</f>
+      <c r="E25" s="16" t="n">
+        <f aca="false">E22+E23+E24</f>
         <v>56530.9828655997</v>
       </c>
-      <c r="F23" s="16" t="n">
-        <f aca="false">F20+F21+F22</f>
+      <c r="F25" s="16" t="n">
+        <f aca="false">F22+F23+F24</f>
         <v>283709.037342633</v>
       </c>
-      <c r="G23" s="16" t="n">
-        <f aca="false">G20+G21+G22</f>
+      <c r="G25" s="16" t="n">
+        <f aca="false">G22+G23+G24</f>
         <v>269517.340478033</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>324</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="16" t="n">
-        <f aca="false">'Returns (Assumed)'!$B$16</f>
-        <v>4558911.31467836</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <f aca="false">'Returns (Assumed)'!$B$18</f>
+        <v>5595076.47991224</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B27" s="10" t="n">
         <f aca="false">-'Returns (Assumed)'!$B$9</f>
         <v>-5095290</v>
       </c>
-      <c r="C25" s="10" t="n">
-        <f aca="false">C23+C24</f>
+      <c r="C27" s="10" t="n">
+        <f aca="false">C25+C26</f>
         <v>571067.714813</v>
       </c>
-      <c r="D25" s="10" t="n">
-        <f aca="false">D23+D24</f>
+      <c r="D27" s="10" t="n">
+        <f aca="false">D25+D26</f>
         <v>392643.86326819</v>
       </c>
-      <c r="E25" s="10" t="n">
-        <f aca="false">E23+E24</f>
+      <c r="E27" s="10" t="n">
+        <f aca="false">E25+E26</f>
         <v>56530.9828655997</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <f aca="false">F23+F24</f>
+      <c r="F27" s="10" t="n">
+        <f aca="false">F25+F26</f>
         <v>283709.037342633</v>
       </c>
-      <c r="G25" s="10" t="n">
-        <f aca="false">G23+G24</f>
-        <v>4828428.65515639</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B27" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>282</v>
-      </c>
-      <c r="B28" s="18" t="n">
-        <f aca="false">IFERROR(IRR(B25:G25),"N/A - no sign change / undefined")</f>
-        <v>0.0436954779740151</v>
+      <c r="G27" s="10" t="n">
+        <f aca="false">G25+G26</f>
+        <v>5864593.82039027</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>284</v>
-      </c>
-      <c r="B29" s="19" t="n">
-        <f aca="false">SUM(C25:G25)/'Returns (Assumed)'!$B$9</f>
-        <v>1.20353900434437</v>
-      </c>
+      <c r="A29" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>326</v>
+        <v>282</v>
       </c>
       <c r="B30" s="18" t="n">
-        <f aca="false">C23/'Returns (Assumed)'!$B$9</f>
+        <f aca="false">IFERROR(IRR(B27:G27),"N/A - no sign change / undefined")</f>
+        <v>0.0807266925391043</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <f aca="false">SUM(C27:G27)/'Returns (Assumed)'!$B$9</f>
+        <v>1.40689645116955</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="B32" s="18" t="n">
+        <f aca="false">C25/'Returns (Assumed)'!$B$9</f>
         <v>0.112077568659095</v>
       </c>
     </row>
@@ -11605,12 +11778,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11635,50 +11808,50 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="16" t="n">
-        <f aca="false">Returns!C$52</f>
-        <v>331713.714813</v>
+        <f aca="false">'Returns (Assumed)'!C$27</f>
+        <v>571067.714813</v>
       </c>
       <c r="D6" s="16" t="n">
-        <f aca="false">Returns!D$52</f>
-        <v>153289.86326819</v>
+        <f aca="false">'Returns (Assumed)'!D$27</f>
+        <v>392643.86326819</v>
       </c>
       <c r="E6" s="16" t="n">
-        <f aca="false">Returns!E$52</f>
-        <v>203911.897210976</v>
+        <f aca="false">'Returns (Assumed)'!E$27</f>
+        <v>56530.9828655997</v>
       </c>
       <c r="F6" s="16" t="n">
-        <f aca="false">Returns!F$52</f>
-        <v>190443.95168801</v>
+        <f aca="false">'Returns (Assumed)'!F$27</f>
+        <v>283709.037342633</v>
       </c>
       <c r="G6" s="16" t="n">
-        <f aca="false">Returns!G$52</f>
-        <v>5035294.43900686</v>
+        <f aca="false">'Returns (Assumed)'!G$27</f>
+        <v>5864593.82039027</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">-Capital!$B$16</f>
-        <v>-4975236</v>
+        <f aca="false">-'Returns (Assumed)'!$B$10</f>
+        <v>-4585761</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="16" t="n">
-        <f aca="false">-Capital!$B$17</f>
-        <v>-552804</v>
+        <f aca="false">-'Returns (Assumed)'!$B$11</f>
+        <v>-509529</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -11688,61 +11861,61 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">Capital!$B$16</f>
-        <v>4975236</v>
+        <f aca="false">'Returns (Assumed)'!$B$10</f>
+        <v>4585761</v>
       </c>
       <c r="C11" s="16" t="n">
         <f aca="false">B11*(1+Assumptions!$C$112)-C12</f>
-        <v>5041541.165187</v>
+        <v>4381554.165187</v>
       </c>
       <c r="D11" s="16" t="n">
         <f aca="false">C11*(1+Assumptions!$C$112)-D12</f>
-        <v>5291574.59513377</v>
+        <v>4339434.63513377</v>
       </c>
       <c r="E11" s="16" t="n">
         <f aca="false">D11*(1+Assumptions!$C$112)-E12</f>
-        <v>5510988.6655335</v>
+        <v>4630058.42307887</v>
       </c>
       <c r="F11" s="16" t="n">
         <f aca="false">E11*(1+Assumptions!$C$112)-F12</f>
-        <v>5761423.80708817</v>
+        <v>4716754.05958255</v>
       </c>
       <c r="G11" s="16" t="n">
         <f aca="false">F11*(1+Assumptions!$C$112)-G12</f>
-        <v>1187043.27264836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C12" s="16" t="n">
         <f aca="false">MIN(C6,B11*(1+Assumptions!$C$112))</f>
-        <v>331713.714813</v>
+        <v>571067.714813</v>
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">MIN(D6,C11*(1+Assumptions!$C$112))</f>
-        <v>153289.86326819</v>
+        <v>392643.86326819</v>
       </c>
       <c r="E12" s="16" t="n">
         <f aca="false">MIN(E6,D11*(1+Assumptions!$C$112))</f>
-        <v>203911.897210976</v>
+        <v>56530.9828655997</v>
       </c>
       <c r="F12" s="16" t="n">
         <f aca="false">MIN(F6,E11*(1+Assumptions!$C$112))</f>
-        <v>190443.95168801</v>
+        <v>283709.037342633</v>
       </c>
       <c r="G12" s="16" t="n">
         <f aca="false">MIN(G6,F11*(1+Assumptions!$C$112))</f>
-        <v>5035294.43900686</v>
+        <v>5094094.38434915</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C14" s="16" t="n">
         <f aca="false">C6-C12</f>
@@ -11762,12 +11935,12 @@
       </c>
       <c r="G14" s="16" t="n">
         <f aca="false">G6-G12</f>
-        <v>0</v>
+        <v>770499.43604112</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -11777,61 +11950,61 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">Capital!$B$16</f>
-        <v>4975236</v>
+        <f aca="false">'Returns (Assumed)'!$B$10</f>
+        <v>4585761</v>
       </c>
       <c r="C17" s="16" t="n">
         <f aca="false">C18-C20</f>
-        <v>5240550.605187</v>
+        <v>4564984.605187</v>
       </c>
       <c r="D17" s="16" t="n">
         <f aca="false">D18-D20</f>
-        <v>5716126.81454125</v>
+        <v>4720138.89454125</v>
       </c>
       <c r="E17" s="16" t="n">
         <f aca="false">E18-E20</f>
-        <v>6198150.13507523</v>
+        <v>5230024.5790206</v>
       </c>
       <c r="F17" s="16" t="n">
         <f aca="false">F18-F20</f>
-        <v>6751484.19959624</v>
+        <v>5573918.49116044</v>
       </c>
       <c r="G17" s="16" t="n">
         <f aca="false">G18-G20</f>
-        <v>2526367.86454093</v>
+        <v>609344.720521759</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C18" s="16" t="n">
         <f aca="false">B17*(1+Assumptions!$C$115)-C12</f>
-        <v>5240550.605187</v>
+        <v>4564984.605187</v>
       </c>
       <c r="D18" s="16" t="n">
         <f aca="false">C17*(1+Assumptions!$C$115)-D12</f>
-        <v>5716126.81454125</v>
+        <v>4720138.89454125</v>
       </c>
       <c r="E18" s="16" t="n">
         <f aca="false">D17*(1+Assumptions!$C$115)-E12</f>
-        <v>6198150.13507523</v>
+        <v>5230024.5790206</v>
       </c>
       <c r="F18" s="16" t="n">
         <f aca="false">E17*(1+Assumptions!$C$115)-F12</f>
-        <v>6751484.19959624</v>
+        <v>5573918.49116044</v>
       </c>
       <c r="G18" s="16" t="n">
         <f aca="false">F17*(1+Assumptions!$C$115)-G12</f>
-        <v>2526367.86454093</v>
+        <v>1148694.32575054</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C19" s="16" t="n">
         <f aca="false">MIN(C14,MAX(0,C18)/Assumptions!$C$113)</f>
@@ -11851,12 +12024,12 @@
       </c>
       <c r="G19" s="16" t="n">
         <f aca="false">MIN(G14,MAX(0,G18)/Assumptions!$C$113)</f>
-        <v>0</v>
+        <v>770499.43604112</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C20" s="16" t="n">
         <f aca="false">C19*Assumptions!$C$113</f>
@@ -11876,12 +12049,12 @@
       </c>
       <c r="G20" s="16" t="n">
         <f aca="false">G19*Assumptions!$C$113</f>
-        <v>0</v>
+        <v>539349.605228784</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C21" s="16" t="n">
         <f aca="false">C19*Assumptions!$C$114</f>
@@ -11901,12 +12074,12 @@
       </c>
       <c r="G21" s="16" t="n">
         <f aca="false">G19*Assumptions!$C$114</f>
-        <v>0</v>
+        <v>231149.830812336</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C22" s="16" t="n">
         <f aca="false">C14-C19</f>
@@ -11931,7 +12104,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -11941,7 +12114,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C25" s="16" t="n">
         <f aca="false">C22</f>
@@ -11966,7 +12139,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C26" s="16" t="n">
         <f aca="false">C25*Assumptions!$C$116</f>
@@ -11991,7 +12164,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C27" s="16" t="n">
         <f aca="false">C25*Assumptions!$C$117</f>
@@ -12016,7 +12189,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -12026,40 +12199,40 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B30" s="16" t="n">
-        <f aca="false">-Capital!$B$16</f>
-        <v>-4975236</v>
+        <f aca="false">-'Returns (Assumed)'!$B$10</f>
+        <v>-4585761</v>
       </c>
       <c r="C30" s="10" t="n">
         <f aca="false">C12+C20+C26</f>
-        <v>331713.714813</v>
+        <v>571067.714813</v>
       </c>
       <c r="D30" s="10" t="n">
         <f aca="false">D12+D20+D26</f>
-        <v>153289.86326819</v>
+        <v>392643.86326819</v>
       </c>
       <c r="E30" s="10" t="n">
         <f aca="false">E12+E20+E26</f>
-        <v>203911.897210976</v>
+        <v>56530.9828655997</v>
       </c>
       <c r="F30" s="10" t="n">
         <f aca="false">F12+F20+F26</f>
-        <v>190443.95168801</v>
+        <v>283709.037342633</v>
       </c>
       <c r="G30" s="10" t="n">
         <f aca="false">G12+G20+G26</f>
-        <v>5035294.43900686</v>
+        <v>5633443.98957794</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B31" s="16" t="n">
-        <f aca="false">-Capital!$B$17</f>
-        <v>-552804</v>
+        <f aca="false">-'Returns (Assumed)'!$B$11</f>
+        <v>-509529</v>
       </c>
       <c r="C31" s="10" t="n">
         <f aca="false">C21+C27</f>
@@ -12079,12 +12252,12 @@
       </c>
       <c r="G31" s="10" t="n">
         <f aca="false">G21+G27</f>
-        <v>0</v>
+        <v>231149.830812336</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -12116,44 +12289,44 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B37" s="18" t="n">
         <f aca="false">IFERROR(IRR(B30:G30),"N/A - no sign change / undefined")</f>
-        <v>0.038533660287425</v>
+        <v>0.0995543216063557</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>352</v>
-      </c>
-      <c r="B38" s="18" t="str">
+        <v>354</v>
+      </c>
+      <c r="B38" s="18" t="n">
         <f aca="false">IFERROR(IRR(B31:G31),"N/A - GP receives $0 in this scenario, IRR undefined")</f>
-        <v>N/A - GP receives $0 in this scenario, IRR undefined</v>
+        <v>-0.14622204957911</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B39" s="19" t="n">
-        <f aca="false">SUM(C30:G30)/Capital!$B$16</f>
-        <v>1.18881875472581</v>
+        <f aca="false">SUM(C30:G30)/'Returns (Assumed)'!$B$10</f>
+        <v>1.51281228739731</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B40" s="19" t="n">
-        <f aca="false">SUM(C31:G31)/Capital!$B$17</f>
-        <v>0</v>
+        <f aca="false">SUM(C31:G31)/'Returns (Assumed)'!$B$11</f>
+        <v>0.45365392511974</v>
       </c>
     </row>
   </sheetData>
